--- a/data/cox_xlsx/HLUNa.CO.xlsx
+++ b/data/cox_xlsx/HLUNa.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="509">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -1075,6 +1075,9 @@
   </si>
   <si>
     <t>Current liabilities</t>
+  </si>
+  <si>
+    <t>Debt LT</t>
   </si>
   <si>
     <t>Deferred tax liabilities</t>
@@ -1668,7 +1671,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1749,6 +1752,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -20947,8 +20953,8 @@
       </c>
     </row>
     <row r="110" ht="15.0" customHeight="1">
-      <c r="A110" s="14" t="s">
-        <v>343</v>
+      <c r="A110" s="27" t="s">
+        <v>352</v>
       </c>
       <c r="B110" s="15"/>
       <c r="C110" s="15"/>
@@ -21094,7 +21100,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B112" s="16">
         <v>8441.0</v>
@@ -21252,7 +21258,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B114" s="15">
         <v>17693.5</v>
@@ -21366,7 +21372,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
@@ -21413,7 +21419,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B117" s="15"/>
       <c r="C117" s="15"/>
@@ -21458,7 +21464,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
@@ -21515,7 +21521,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B119" s="16">
         <v>757.73</v>
@@ -21609,7 +21615,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B121" s="16">
         <v>145.53</v>
@@ -21703,7 +21709,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B123" s="18">
         <v>28945.53</v>
@@ -21792,7 +21798,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B124" s="18">
         <v>42950.05</v>
@@ -21881,7 +21887,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B125" s="16">
         <v>1575.57</v>
@@ -21970,7 +21976,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B126" s="22">
         <v>-1229.13</v>
@@ -22039,7 +22045,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B127" s="16">
         <v>112.31</v>
@@ -22106,7 +22112,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B128" s="15">
         <v>38935.2</v>
@@ -22195,7 +22201,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B129" s="15"/>
       <c r="C129" s="15"/>
@@ -22307,7 +22313,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B131" s="15"/>
       <c r="C131" s="15"/>
@@ -22346,7 +22352,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B132" s="15"/>
       <c r="C132" s="15"/>
@@ -22381,7 +22387,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B133" s="18">
         <v>39393.95</v>
@@ -22470,7 +22476,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="17" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B134" s="18">
         <v>39393.95</v>
@@ -22559,7 +22565,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B135" s="18">
         <v>82344.0</v>
@@ -22648,7 +22654,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B136" s="16">
         <v>992.15</v>
@@ -22737,7 +22743,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B137" s="16">
         <v>995.74</v>
@@ -22826,7 +22832,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B138" s="20">
         <v>3.59</v>
@@ -22915,7 +22921,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B139" s="15">
         <v>17693.5</v>
@@ -22984,7 +22990,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B140" s="15"/>
       <c r="C140" s="15"/>
@@ -23041,7 +23047,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B141" s="15"/>
       <c r="C141" s="15"/>
@@ -23078,7 +23084,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B142" s="15"/>
       <c r="C142" s="15"/>
@@ -23119,7 +23125,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B143" s="15"/>
       <c r="C143" s="15"/>
@@ -23170,7 +23176,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B144" s="15"/>
       <c r="C144" s="15"/>
@@ -23215,7 +23221,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
@@ -23262,7 +23268,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B146" s="15"/>
       <c r="C146" s="15"/>
@@ -23313,7 +23319,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B147" s="15">
         <v>17693.5</v>
@@ -23372,7 +23378,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B148" s="15"/>
       <c r="C148" s="15"/>
@@ -23415,7 +23421,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
@@ -23458,7 +23464,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
@@ -23501,7 +23507,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
@@ -23544,7 +23550,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -23579,7 +23585,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B153" s="15"/>
       <c r="C153" s="15"/>
@@ -23614,7 +23620,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B154" s="15"/>
       <c r="C154" s="15"/>
@@ -23695,7 +23701,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
@@ -23776,7 +23782,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B156" s="15"/>
       <c r="C156" s="15"/>
@@ -23857,7 +23863,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -23938,7 +23944,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B158" s="20">
         <v>3.46</v>
@@ -23979,7 +23985,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B159" s="16">
         <v>793.13</v>
@@ -24020,7 +24026,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B160" s="16">
         <v>796.59</v>
@@ -24061,7 +24067,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B161" s="20">
         <v>0.8</v>
@@ -24102,7 +24108,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B162" s="16">
         <v>199.02</v>
@@ -24143,7 +24149,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B163" s="20">
         <v>0.2</v>
@@ -24184,7 +24190,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B164" s="16">
         <v>199.15</v>
@@ -24225,7 +24231,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B165" s="20">
         <v>0.13</v>
@@ -25120,7 +25126,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -25584,88 +25590,88 @@
         <v>50</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="X15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AC15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -25759,7 +25765,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -25881,7 +25887,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B20" s="16">
         <v>8272.88</v>
@@ -25968,7 +25974,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="16">
@@ -26037,7 +26043,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B22" s="16">
         <v>2924.91</v>
@@ -26072,7 +26078,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B23" s="16">
         <v>1010.0</v>
@@ -26109,7 +26115,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B24" s="20">
         <v>69.01</v>
@@ -26154,7 +26160,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B25" s="16">
         <v>192.9</v>
@@ -26199,7 +26205,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B26" s="22">
         <v>-672.81</v>
@@ -26272,7 +26278,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -26321,7 +26327,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -26356,7 +26362,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B29" s="22">
         <v>-882.96</v>
@@ -26439,7 +26445,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B30" s="16">
         <v>340.33</v>
@@ -26522,7 +26528,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B31" s="15">
         <v>10826.1</v>
@@ -26581,7 +26587,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B32" s="22">
         <v>-2230.15</v>
@@ -26664,7 +26670,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -26717,7 +26723,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -26774,7 +26780,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -26833,7 +26839,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -26872,7 +26878,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -26913,7 +26919,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B38" s="22">
         <v>-556.75</v>
@@ -26984,7 +26990,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B39" s="22">
         <v>-785.73</v>
@@ -27055,7 +27061,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B40" s="15">
         <v>0.0</v>
@@ -27092,7 +27098,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B41" s="16">
         <v>914.33</v>
@@ -27163,7 +27169,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -27222,7 +27228,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -27259,7 +27265,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -27316,7 +27322,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -27363,7 +27369,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B46" s="19">
         <v>8595.95</v>
@@ -27452,7 +27458,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B47" s="15">
         <v>0.0</v>
@@ -27517,7 +27523,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -27566,7 +27572,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -27613,7 +27619,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -27682,7 +27688,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -27745,7 +27751,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B52" s="22">
         <v>-100.37</v>
@@ -27816,7 +27822,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B53" s="22">
         <v>-868.85</v>
@@ -27901,7 +27907,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B54" s="20">
         <v>10.98</v>
@@ -27986,7 +27992,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -28025,7 +28031,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B56" s="15">
         <v>0.0</v>
@@ -28078,7 +28084,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -28115,7 +28121,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -28156,12 +28162,12 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B59" s="23">
         <v>-958.24</v>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="28">
         <v>-23818.89</v>
       </c>
       <c r="D59" s="23">
@@ -28176,7 +28182,7 @@
       <c r="G59" s="23">
         <v>-671.96</v>
       </c>
-      <c r="H59" s="27">
+      <c r="H59" s="28">
         <v>-10227.35</v>
       </c>
       <c r="I59" s="23">
@@ -28245,7 +28251,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B60" s="16">
         <v>5827.87</v>
@@ -28326,7 +28332,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B61" s="26">
         <v>-13691.42</v>
@@ -28403,7 +28409,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B62" s="22">
         <v>-1478.92</v>
@@ -28488,7 +28494,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -28547,7 +28553,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -28618,7 +28624,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B65" s="21">
         <v>-31.37</v>
@@ -28738,7 +28744,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B67" s="22">
         <v>-133.31</v>
@@ -28785,7 +28791,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -28832,7 +28838,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="17" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B69" s="23">
         <v>-9507.15</v>
@@ -28921,7 +28927,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B70" s="16">
         <v>7377.96</v>
@@ -29008,7 +29014,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B71" s="21">
         <v>-61.16</v>
@@ -29097,7 +29103,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B72" s="22">
         <v>-1869.44</v>
@@ -29243,7 +29249,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="17" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B74" s="23">
         <v>-1930.6</v>
@@ -29332,7 +29338,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B75" s="16">
         <v>7637.71</v>
@@ -30321,7 +30327,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -30513,13 +30519,13 @@
         <v>44</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AF11" s="7" t="s">
         <v>45</v>
@@ -31017,7 +31023,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -31137,3207 +31143,3207 @@
         <v>82</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AF19" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>460</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29"/>
-      <c r="Y20" s="29"/>
-      <c r="Z20" s="29"/>
-      <c r="AA20" s="29"/>
-      <c r="AB20" s="29"/>
-      <c r="AC20" s="29"/>
-      <c r="AD20" s="29"/>
-      <c r="AE20" s="29"/>
-      <c r="AF20" s="29"/>
+      <c r="A20" s="29" t="s">
+        <v>461</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="30"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>460</v>
-      </c>
-      <c r="B21" s="31">
+      <c r="A21" s="31" t="s">
+        <v>461</v>
+      </c>
+      <c r="B21" s="32">
         <v>78795.99</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <v>81422.62</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <v>46446.82</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <v>38835.0</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <v>49374.58</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <v>64130.3</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <v>75406.2</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="32">
         <v>66689.39</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="32">
         <v>78153.16</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="32">
         <v>69028.44</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="32">
         <v>62639.01</v>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="32">
         <v>28882.48</v>
       </c>
-      <c r="N21" s="31">
+      <c r="N21" s="32">
         <v>25913.3</v>
       </c>
-      <c r="O21" s="31">
+      <c r="O21" s="32">
         <v>14142.49</v>
       </c>
-      <c r="P21" s="31">
+      <c r="P21" s="32">
         <v>19939.01</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="32">
         <v>21277.93</v>
       </c>
-      <c r="R21" s="31">
+      <c r="R21" s="32">
         <v>22338.88</v>
       </c>
-      <c r="S21" s="31">
+      <c r="S21" s="32">
         <v>25713.63</v>
       </c>
-      <c r="T21" s="31">
+      <c r="T21" s="32">
         <v>28939.66</v>
       </c>
-      <c r="U21" s="31">
+      <c r="U21" s="32">
         <v>35500.41</v>
       </c>
-      <c r="V21" s="31">
+      <c r="V21" s="32">
         <v>29354.73</v>
       </c>
-      <c r="W21" s="31">
+      <c r="W21" s="32">
         <v>28953.43</v>
       </c>
-      <c r="X21" s="31">
+      <c r="X21" s="32">
         <v>24928.86</v>
       </c>
-      <c r="Y21" s="31">
+      <c r="Y21" s="32">
         <v>42454.24</v>
       </c>
-      <c r="Z21" s="31">
+      <c r="Z21" s="32">
         <v>52792.98</v>
       </c>
-      <c r="AA21" s="31">
+      <c r="AA21" s="32">
         <v>48812.28</v>
       </c>
-      <c r="AB21" s="31">
+      <c r="AB21" s="32">
         <v>17116.6</v>
       </c>
-      <c r="AC21" s="31"/>
-      <c r="AD21" s="31"/>
-      <c r="AE21" s="31"/>
-      <c r="AF21" s="31"/>
+      <c r="AC21" s="32"/>
+      <c r="AD21" s="32"/>
+      <c r="AE21" s="32"/>
+      <c r="AF21" s="32"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>461</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="A22" s="31" t="s">
+        <v>462</v>
+      </c>
+      <c r="B22" s="32">
         <v>62189.67</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <v>60694.48</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <v>59402.64</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <v>61272.92</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <v>66997.26</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <v>75627.92</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <v>71607.31</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="32">
         <v>63232.48</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="32">
         <v>55876.14</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="32">
         <v>40712.71</v>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="32">
         <v>33237.6</v>
       </c>
-      <c r="M22" s="31">
+      <c r="M22" s="32">
         <v>24488.06</v>
       </c>
-      <c r="N22" s="31">
+      <c r="N22" s="32">
         <v>21711.28</v>
       </c>
-      <c r="O22" s="31">
+      <c r="O22" s="32">
         <v>18433.99</v>
       </c>
-      <c r="P22" s="31">
+      <c r="P22" s="32">
         <v>22159.02</v>
       </c>
-      <c r="Q22" s="31">
+      <c r="Q22" s="32">
         <v>24973.72</v>
       </c>
-      <c r="R22" s="31">
+      <c r="R22" s="32">
         <v>28210.86</v>
       </c>
-      <c r="S22" s="31">
+      <c r="S22" s="32">
         <v>34603.85</v>
       </c>
-      <c r="T22" s="31">
+      <c r="T22" s="32">
         <v>28733.3</v>
       </c>
-      <c r="U22" s="31">
+      <c r="U22" s="32">
         <v>33362.87</v>
       </c>
-      <c r="V22" s="31">
+      <c r="V22" s="32">
         <v>36030.37</v>
       </c>
-      <c r="W22" s="31">
+      <c r="W22" s="32">
         <v>40978.6</v>
       </c>
-      <c r="X22" s="31">
+      <c r="X22" s="32">
         <v>39327.74</v>
       </c>
-      <c r="Y22" s="31"/>
-      <c r="Z22" s="31"/>
-      <c r="AA22" s="31"/>
-      <c r="AB22" s="31"/>
-      <c r="AC22" s="31"/>
-      <c r="AD22" s="31"/>
-      <c r="AE22" s="31"/>
-      <c r="AF22" s="31"/>
+      <c r="Y22" s="32"/>
+      <c r="Z22" s="32"/>
+      <c r="AA22" s="32"/>
+      <c r="AB22" s="32"/>
+      <c r="AC22" s="32"/>
+      <c r="AD22" s="32"/>
+      <c r="AE22" s="32"/>
+      <c r="AF22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>462</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="29"/>
-      <c r="Z23" s="29"/>
-      <c r="AA23" s="29"/>
-      <c r="AB23" s="29"/>
-      <c r="AC23" s="29"/>
-      <c r="AD23" s="29"/>
-      <c r="AE23" s="29"/>
-      <c r="AF23" s="29"/>
+      <c r="A23" s="29" t="s">
+        <v>463</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="30"/>
+      <c r="AE23" s="30"/>
+      <c r="AF23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>462</v>
-      </c>
-      <c r="B24" s="31">
+      <c r="A24" s="31" t="s">
+        <v>463</v>
+      </c>
+      <c r="B24" s="32">
         <v>65791.22</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>62439.81</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <v>47735.8</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <v>35970.8</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <v>45277.22</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <v>58546.31</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <v>66754.29</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="32">
         <v>75397.48</v>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="32">
         <v>82941.83</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="32">
         <v>69420.93</v>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="32">
         <v>59745.93</v>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="32">
         <v>29278.26</v>
       </c>
-      <c r="N24" s="31">
+      <c r="N24" s="32">
         <v>30049.77</v>
       </c>
-      <c r="O24" s="31">
+      <c r="O24" s="32">
         <v>16005.95</v>
       </c>
-      <c r="P24" s="31">
+      <c r="P24" s="32">
         <v>22044.3</v>
       </c>
-      <c r="Q24" s="31">
+      <c r="Q24" s="32">
         <v>21727.35</v>
       </c>
-      <c r="R24" s="31">
+      <c r="R24" s="32">
         <v>20715.7</v>
       </c>
-      <c r="S24" s="31">
+      <c r="S24" s="32">
         <v>28256.49</v>
       </c>
-      <c r="T24" s="31">
+      <c r="T24" s="32">
         <v>30434.1</v>
       </c>
-      <c r="U24" s="31">
+      <c r="U24" s="32">
         <v>36467.07</v>
       </c>
-      <c r="V24" s="31">
+      <c r="V24" s="32">
         <v>31753.44</v>
       </c>
-      <c r="W24" s="31">
+      <c r="W24" s="32">
         <v>31604.69</v>
       </c>
-      <c r="X24" s="31">
+      <c r="X24" s="32">
         <v>25808.22</v>
       </c>
-      <c r="Y24" s="31">
+      <c r="Y24" s="32">
         <v>43063.39</v>
       </c>
-      <c r="Z24" s="31">
+      <c r="Z24" s="32">
         <v>53725.41</v>
       </c>
-      <c r="AA24" s="31">
+      <c r="AA24" s="32">
         <v>50365.19</v>
       </c>
-      <c r="AB24" s="31">
+      <c r="AB24" s="32">
         <v>18643.31</v>
       </c>
-      <c r="AC24" s="31"/>
-      <c r="AD24" s="31"/>
-      <c r="AE24" s="31"/>
-      <c r="AF24" s="31"/>
+      <c r="AC24" s="32"/>
+      <c r="AD24" s="32"/>
+      <c r="AE24" s="32"/>
+      <c r="AF24" s="32"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>463</v>
-      </c>
-      <c r="B25" s="31">
+      <c r="A25" s="31" t="s">
+        <v>464</v>
+      </c>
+      <c r="B25" s="32">
         <v>54449.45</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <v>54315.85</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <v>54976.88</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <v>58722.36</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <v>66083.8</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="32">
         <v>75620.04</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <v>72052.42</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="32">
         <v>65509.61</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="32">
         <v>57388.94</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="32">
         <v>41688.68</v>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="32">
         <v>34702.28</v>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="32">
         <v>26520.84</v>
       </c>
-      <c r="N25" s="31">
+      <c r="N25" s="32">
         <v>23184.76</v>
       </c>
-      <c r="O25" s="31">
+      <c r="O25" s="32">
         <v>19386.69</v>
       </c>
-      <c r="P25" s="31">
+      <c r="P25" s="32">
         <v>23064.53</v>
       </c>
-      <c r="Q25" s="31">
+      <c r="Q25" s="32">
         <v>25643.36</v>
       </c>
-      <c r="R25" s="31">
+      <c r="R25" s="32">
         <v>29328.69</v>
       </c>
-      <c r="S25" s="31">
+      <c r="S25" s="32">
         <v>36916.22</v>
       </c>
-      <c r="T25" s="31">
+      <c r="T25" s="32">
         <v>30370.35</v>
       </c>
-      <c r="U25" s="31">
+      <c r="U25" s="32">
         <v>34888.12</v>
       </c>
-      <c r="V25" s="31">
+      <c r="V25" s="32">
         <v>37509.03</v>
       </c>
-      <c r="W25" s="31">
+      <c r="W25" s="32">
         <v>42323.09</v>
       </c>
-      <c r="X25" s="31">
+      <c r="X25" s="32">
         <v>40472.7</v>
       </c>
-      <c r="Y25" s="31"/>
-      <c r="Z25" s="31"/>
-      <c r="AA25" s="31"/>
-      <c r="AB25" s="31"/>
-      <c r="AC25" s="31"/>
-      <c r="AD25" s="31"/>
-      <c r="AE25" s="31"/>
-      <c r="AF25" s="31"/>
+      <c r="Y25" s="32"/>
+      <c r="Z25" s="32"/>
+      <c r="AA25" s="32"/>
+      <c r="AB25" s="32"/>
+      <c r="AC25" s="32"/>
+      <c r="AD25" s="32"/>
+      <c r="AE25" s="32"/>
+      <c r="AF25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>464</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="29"/>
-      <c r="AD26" s="29"/>
-      <c r="AE26" s="29"/>
-      <c r="AF26" s="29"/>
+      <c r="A26" s="29" t="s">
+        <v>465</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>465</v>
-      </c>
-      <c r="B27" s="32">
+      <c r="A27" s="31" t="s">
+        <v>466</v>
+      </c>
+      <c r="B27" s="33">
         <v>57.26</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>52.71</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <v>43.07</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="33">
         <v>33.68</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="34">
         <v>227.35</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="34">
         <v>293.98</v>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="34">
         <v>335.22</v>
       </c>
-      <c r="I27" s="33">
+      <c r="I27" s="34">
         <v>378.68</v>
       </c>
-      <c r="J27" s="33">
+      <c r="J27" s="34">
         <v>416.69</v>
       </c>
-      <c r="K27" s="33">
+      <c r="K27" s="34">
         <v>351.29</v>
       </c>
-      <c r="L27" s="33">
+      <c r="L27" s="34">
         <v>302.82</v>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="34">
         <v>149.08</v>
       </c>
-      <c r="N27" s="33">
+      <c r="N27" s="34">
         <v>153.16</v>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="33">
         <v>81.61</v>
       </c>
-      <c r="P27" s="33">
+      <c r="P27" s="34">
         <v>112.39</v>
       </c>
-      <c r="Q27" s="33">
+      <c r="Q27" s="34">
         <v>110.79</v>
       </c>
-      <c r="R27" s="33">
+      <c r="R27" s="34">
         <v>105.63</v>
       </c>
-      <c r="S27" s="33">
+      <c r="S27" s="34">
         <v>143.52</v>
       </c>
-      <c r="T27" s="33">
+      <c r="T27" s="34">
         <v>146.83</v>
       </c>
-      <c r="U27" s="33">
+      <c r="U27" s="34">
         <v>171.89</v>
       </c>
-      <c r="V27" s="33">
+      <c r="V27" s="34">
         <v>139.75</v>
       </c>
-      <c r="W27" s="33">
+      <c r="W27" s="34">
         <v>135.21</v>
       </c>
-      <c r="X27" s="33">
+      <c r="X27" s="34">
         <v>110.41</v>
       </c>
-      <c r="Y27" s="33">
+      <c r="Y27" s="34">
         <v>184.23</v>
       </c>
-      <c r="Z27" s="33">
+      <c r="Z27" s="34">
         <v>230.48</v>
       </c>
-      <c r="AA27" s="33">
+      <c r="AA27" s="34">
         <v>216.07</v>
       </c>
-      <c r="AB27" s="32">
+      <c r="AB27" s="33">
         <v>79.98</v>
       </c>
-      <c r="AC27" s="31"/>
-      <c r="AD27" s="31"/>
-      <c r="AE27" s="31"/>
-      <c r="AF27" s="31"/>
+      <c r="AC27" s="32"/>
+      <c r="AD27" s="32"/>
+      <c r="AE27" s="32"/>
+      <c r="AF27" s="32"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>466</v>
-      </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="33">
+      <c r="A28" s="31" t="s">
+        <v>467</v>
+      </c>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="34">
         <v>331.9</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="34">
         <v>380.4</v>
       </c>
-      <c r="H28" s="33">
+      <c r="H28" s="34">
         <v>363.02</v>
       </c>
-      <c r="I28" s="33">
+      <c r="I28" s="34">
         <v>330.62</v>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="34">
         <v>290.36</v>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="34">
         <v>211.63</v>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="34">
         <v>176.52</v>
       </c>
-      <c r="M28" s="33">
+      <c r="M28" s="34">
         <v>135.17</v>
       </c>
-      <c r="N28" s="33">
+      <c r="N28" s="34">
         <v>118.2</v>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="33">
         <v>98.76</v>
       </c>
-      <c r="P28" s="33">
+      <c r="P28" s="34">
         <v>115.88</v>
       </c>
-      <c r="Q28" s="33">
+      <c r="Q28" s="34">
         <v>126.36</v>
       </c>
-      <c r="R28" s="33">
+      <c r="R28" s="34">
         <v>140.24</v>
       </c>
-      <c r="S28" s="33">
+      <c r="S28" s="34">
         <v>171.24</v>
       </c>
-      <c r="T28" s="33">
+      <c r="T28" s="34">
         <v>137.09</v>
       </c>
-      <c r="U28" s="33">
+      <c r="U28" s="34">
         <v>153.24</v>
       </c>
-      <c r="V28" s="33">
+      <c r="V28" s="34">
         <v>161.38</v>
       </c>
-      <c r="W28" s="33">
+      <c r="W28" s="34">
         <v>181.32</v>
       </c>
-      <c r="X28" s="33">
+      <c r="X28" s="34">
         <v>173.45</v>
       </c>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="31"/>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="31"/>
-      <c r="AC28" s="31"/>
-      <c r="AD28" s="31"/>
-      <c r="AE28" s="31"/>
-      <c r="AF28" s="31"/>
+      <c r="Y28" s="32"/>
+      <c r="Z28" s="32"/>
+      <c r="AA28" s="32"/>
+      <c r="AB28" s="32"/>
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="32"/>
+      <c r="AE28" s="32"/>
+      <c r="AF28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>467</v>
-      </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
-      <c r="Y29" s="29"/>
-      <c r="Z29" s="29"/>
-      <c r="AA29" s="29"/>
-      <c r="AB29" s="29"/>
-      <c r="AC29" s="29"/>
-      <c r="AD29" s="29"/>
-      <c r="AE29" s="29"/>
-      <c r="AF29" s="29"/>
+      <c r="A29" s="29" t="s">
+        <v>468</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
+      <c r="AE29" s="30"/>
+      <c r="AF29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>468</v>
-      </c>
-      <c r="B30" s="34">
+      <c r="A30" s="31" t="s">
+        <v>469</v>
+      </c>
+      <c r="B30" s="35">
         <v>13.54</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>8.34</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="35">
         <v>12.57</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="35">
         <v>11.38</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="35">
         <v>4.95</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="35">
         <v>8.09</v>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="35">
         <v>4.28</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="35">
         <v>9.3</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="35">
         <v>5.33</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="35">
         <v>4.91</v>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="36">
         <v>-5.97</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="35">
         <v>0.25</v>
       </c>
-      <c r="N30" s="34">
+      <c r="N30" s="35">
         <v>8.35</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="35">
         <v>2.95</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="35">
         <v>9.5</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="35">
         <v>11.73</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="35">
         <v>9.67</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="35">
         <v>7.97</v>
       </c>
-      <c r="T30" s="34">
+      <c r="T30" s="35">
         <v>6.87</v>
       </c>
-      <c r="U30" s="34">
+      <c r="U30" s="35">
         <v>1.87</v>
       </c>
-      <c r="V30" s="34">
+      <c r="V30" s="35">
         <v>4.95</v>
       </c>
-      <c r="W30" s="34">
+      <c r="W30" s="35">
         <v>8.38</v>
       </c>
-      <c r="X30" s="34">
+      <c r="X30" s="35">
         <v>3.58</v>
       </c>
-      <c r="Y30" s="34">
+      <c r="Y30" s="35">
         <v>0.56</v>
       </c>
-      <c r="Z30" s="34">
+      <c r="Z30" s="35">
         <v>1.35</v>
       </c>
-      <c r="AA30" s="34">
+      <c r="AA30" s="35">
         <v>1.01</v>
       </c>
-      <c r="AB30" s="34"/>
-      <c r="AC30" s="34"/>
-      <c r="AD30" s="34"/>
-      <c r="AE30" s="34"/>
-      <c r="AF30" s="34"/>
+      <c r="AB30" s="35"/>
+      <c r="AC30" s="35"/>
+      <c r="AD30" s="35"/>
+      <c r="AE30" s="35"/>
+      <c r="AF30" s="35"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
-        <v>469</v>
-      </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34">
+      <c r="A31" s="31" t="s">
+        <v>470</v>
+      </c>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35">
         <v>6.45</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="35">
         <v>6.31</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="35">
         <v>3.94</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="35">
         <v>3.51</v>
       </c>
-      <c r="J31" s="34">
+      <c r="J31" s="35">
         <v>2.61</v>
       </c>
-      <c r="K31" s="34">
+      <c r="K31" s="35">
         <v>1.65</v>
       </c>
-      <c r="L31" s="34">
+      <c r="L31" s="35">
         <v>1.52</v>
       </c>
-      <c r="M31" s="34">
+      <c r="M31" s="35">
         <v>6.63</v>
       </c>
-      <c r="N31" s="34">
+      <c r="N31" s="35">
         <v>8.65</v>
       </c>
-      <c r="O31" s="34">
+      <c r="O31" s="35">
         <v>8.59</v>
       </c>
-      <c r="P31" s="34">
+      <c r="P31" s="35">
         <v>9.0</v>
       </c>
-      <c r="Q31" s="34">
+      <c r="Q31" s="35">
         <v>7.07</v>
       </c>
-      <c r="R31" s="34">
+      <c r="R31" s="35">
         <v>5.85</v>
       </c>
-      <c r="S31" s="34">
+      <c r="S31" s="35">
         <v>5.77</v>
       </c>
-      <c r="T31" s="34">
+      <c r="T31" s="35">
         <v>5.06</v>
       </c>
-      <c r="U31" s="34">
+      <c r="U31" s="35">
         <v>3.48</v>
       </c>
-      <c r="V31" s="34">
+      <c r="V31" s="35">
         <v>3.21</v>
       </c>
-      <c r="W31" s="34">
+      <c r="W31" s="35">
         <v>2.4</v>
       </c>
-      <c r="X31" s="34"/>
-      <c r="Y31" s="34"/>
-      <c r="Z31" s="34"/>
-      <c r="AA31" s="34"/>
-      <c r="AB31" s="34"/>
-      <c r="AC31" s="34"/>
-      <c r="AD31" s="34"/>
-      <c r="AE31" s="34"/>
-      <c r="AF31" s="34"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35"/>
+      <c r="AA31" s="35"/>
+      <c r="AB31" s="35"/>
+      <c r="AC31" s="35"/>
+      <c r="AD31" s="35"/>
+      <c r="AE31" s="35"/>
+      <c r="AF31" s="35"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>470</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
-      <c r="Z32" s="29"/>
-      <c r="AA32" s="29"/>
-      <c r="AB32" s="29"/>
-      <c r="AC32" s="29"/>
-      <c r="AD32" s="29"/>
-      <c r="AE32" s="29"/>
-      <c r="AF32" s="29"/>
+      <c r="A32" s="29" t="s">
+        <v>471</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="30" t="s">
-        <v>471</v>
-      </c>
-      <c r="B33" s="34">
+      <c r="A33" s="31" t="s">
+        <v>472</v>
+      </c>
+      <c r="B33" s="35">
         <v>2.62</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="35">
         <v>2.1</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="35">
         <v>2.02</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="35">
         <v>0.0</v>
       </c>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-      <c r="U33" s="34"/>
-      <c r="V33" s="34"/>
-      <c r="W33" s="34"/>
-      <c r="X33" s="34"/>
-      <c r="Y33" s="34"/>
-      <c r="Z33" s="34"/>
-      <c r="AA33" s="34"/>
-      <c r="AB33" s="34"/>
-      <c r="AC33" s="34"/>
-      <c r="AD33" s="34"/>
-      <c r="AE33" s="34"/>
-      <c r="AF33" s="34"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="35"/>
+      <c r="R33" s="35"/>
+      <c r="S33" s="35"/>
+      <c r="T33" s="35"/>
+      <c r="U33" s="35"/>
+      <c r="V33" s="35"/>
+      <c r="W33" s="35"/>
+      <c r="X33" s="35"/>
+      <c r="Y33" s="35"/>
+      <c r="Z33" s="35"/>
+      <c r="AA33" s="35"/>
+      <c r="AB33" s="35"/>
+      <c r="AC33" s="35"/>
+      <c r="AD33" s="35"/>
+      <c r="AE33" s="35"/>
+      <c r="AF33" s="35"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
-        <v>472</v>
-      </c>
-      <c r="B34" s="34">
+      <c r="A34" s="31" t="s">
+        <v>473</v>
+      </c>
+      <c r="B34" s="35">
         <v>2.62</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="35">
         <v>2.1</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="35">
         <v>2.02</v>
       </c>
-      <c r="E34" s="34">
+      <c r="E34" s="35">
         <v>0.0</v>
       </c>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="34"/>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-      <c r="U34" s="34"/>
-      <c r="V34" s="34"/>
-      <c r="W34" s="34"/>
-      <c r="X34" s="34"/>
-      <c r="Y34" s="34"/>
-      <c r="Z34" s="34"/>
-      <c r="AA34" s="34"/>
-      <c r="AB34" s="34"/>
-      <c r="AC34" s="34"/>
-      <c r="AD34" s="34"/>
-      <c r="AE34" s="34"/>
-      <c r="AF34" s="34"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="35"/>
+      <c r="R34" s="35"/>
+      <c r="S34" s="35"/>
+      <c r="T34" s="35"/>
+      <c r="U34" s="35"/>
+      <c r="V34" s="35"/>
+      <c r="W34" s="35"/>
+      <c r="X34" s="35"/>
+      <c r="Y34" s="35"/>
+      <c r="Z34" s="35"/>
+      <c r="AA34" s="35"/>
+      <c r="AB34" s="35"/>
+      <c r="AC34" s="35"/>
+      <c r="AD34" s="35"/>
+      <c r="AE34" s="35"/>
+      <c r="AF34" s="35"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>473</v>
-      </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="29"/>
-      <c r="L35" s="29"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
-      <c r="O35" s="29"/>
-      <c r="P35" s="29"/>
-      <c r="Q35" s="29"/>
-      <c r="R35" s="29"/>
-      <c r="S35" s="29"/>
-      <c r="T35" s="29"/>
-      <c r="U35" s="29"/>
-      <c r="V35" s="29"/>
-      <c r="W35" s="29"/>
-      <c r="X35" s="29"/>
-      <c r="Y35" s="29"/>
-      <c r="Z35" s="29"/>
-      <c r="AA35" s="29"/>
-      <c r="AB35" s="29"/>
-      <c r="AC35" s="29"/>
-      <c r="AD35" s="29"/>
-      <c r="AE35" s="29"/>
-      <c r="AF35" s="29"/>
+      <c r="A35" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="30"/>
+      <c r="S35" s="30"/>
+      <c r="T35" s="30"/>
+      <c r="U35" s="30"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="30"/>
+      <c r="X35" s="30"/>
+      <c r="Y35" s="30"/>
+      <c r="Z35" s="30"/>
+      <c r="AA35" s="30"/>
+      <c r="AB35" s="30"/>
+      <c r="AC35" s="30"/>
+      <c r="AD35" s="30"/>
+      <c r="AE35" s="30"/>
+      <c r="AF35" s="30"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
-        <v>474</v>
-      </c>
-      <c r="B36" s="32">
+      <c r="A36" s="31" t="s">
+        <v>475</v>
+      </c>
+      <c r="B36" s="33">
         <v>1.44</v>
       </c>
-      <c r="C36" s="32">
+      <c r="C36" s="33">
         <v>1.32</v>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="33">
         <v>1.29</v>
       </c>
-      <c r="E36" s="32">
+      <c r="E36" s="33">
         <v>1.14</v>
       </c>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31"/>
-      <c r="L36" s="31"/>
-      <c r="M36" s="31"/>
-      <c r="N36" s="31"/>
-      <c r="O36" s="31"/>
-      <c r="P36" s="31"/>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="31"/>
-      <c r="S36" s="31"/>
-      <c r="T36" s="31"/>
-      <c r="U36" s="31"/>
-      <c r="V36" s="31"/>
-      <c r="W36" s="31"/>
-      <c r="X36" s="31"/>
-      <c r="Y36" s="31"/>
-      <c r="Z36" s="31"/>
-      <c r="AA36" s="31"/>
-      <c r="AB36" s="31"/>
-      <c r="AC36" s="31"/>
-      <c r="AD36" s="31"/>
-      <c r="AE36" s="31"/>
-      <c r="AF36" s="31"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="32"/>
+      <c r="V36" s="32"/>
+      <c r="W36" s="32"/>
+      <c r="X36" s="32"/>
+      <c r="Y36" s="32"/>
+      <c r="Z36" s="32"/>
+      <c r="AA36" s="32"/>
+      <c r="AB36" s="32"/>
+      <c r="AC36" s="32"/>
+      <c r="AD36" s="32"/>
+      <c r="AE36" s="32"/>
+      <c r="AF36" s="32"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
-        <v>475</v>
-      </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
-      <c r="Y37" s="29"/>
-      <c r="Z37" s="29"/>
-      <c r="AA37" s="29"/>
-      <c r="AB37" s="29"/>
-      <c r="AC37" s="29"/>
-      <c r="AD37" s="29"/>
-      <c r="AE37" s="29"/>
-      <c r="AF37" s="29"/>
+      <c r="A37" s="29" t="s">
+        <v>476</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+      <c r="AA37" s="30"/>
+      <c r="AB37" s="30"/>
+      <c r="AC37" s="30"/>
+      <c r="AD37" s="30"/>
+      <c r="AE37" s="30"/>
+      <c r="AF37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
-        <v>476</v>
-      </c>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="32">
+      <c r="A38" s="31" t="s">
+        <v>477</v>
+      </c>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="33">
         <v>21.04</v>
       </c>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="32">
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="33">
         <v>9.11</v>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="33">
         <v>13.56</v>
       </c>
-      <c r="K38" s="32">
+      <c r="K38" s="33">
         <v>66.31</v>
       </c>
-      <c r="L38" s="31"/>
-      <c r="M38" s="32">
+      <c r="L38" s="32"/>
+      <c r="M38" s="33">
         <v>28.17</v>
       </c>
-      <c r="N38" s="32">
+      <c r="N38" s="33">
         <v>6.1</v>
       </c>
-      <c r="O38" s="32">
+      <c r="O38" s="33">
         <v>3.9</v>
       </c>
-      <c r="P38" s="32">
+      <c r="P38" s="33">
         <v>4.89</v>
       </c>
-      <c r="Q38" s="32">
+      <c r="Q38" s="33">
         <v>6.42</v>
       </c>
-      <c r="R38" s="32">
+      <c r="R38" s="33">
         <v>17.22</v>
       </c>
-      <c r="S38" s="32">
+      <c r="S38" s="33">
         <v>4.2</v>
       </c>
-      <c r="T38" s="32">
+      <c r="T38" s="33">
         <v>5.03</v>
       </c>
-      <c r="U38" s="32">
+      <c r="U38" s="33">
         <v>7.34</v>
       </c>
-      <c r="V38" s="32">
+      <c r="V38" s="33">
         <v>4.93</v>
       </c>
-      <c r="W38" s="32">
+      <c r="W38" s="33">
         <v>3.55</v>
       </c>
-      <c r="X38" s="32">
+      <c r="X38" s="33">
         <v>3.21</v>
       </c>
-      <c r="Y38" s="32">
+      <c r="Y38" s="33">
         <v>5.18</v>
       </c>
-      <c r="Z38" s="32">
+      <c r="Z38" s="33">
         <v>10.46</v>
       </c>
-      <c r="AA38" s="32">
+      <c r="AA38" s="33">
         <v>12.06</v>
       </c>
-      <c r="AB38" s="32">
+      <c r="AB38" s="33">
         <v>5.88</v>
       </c>
-      <c r="AC38" s="31"/>
-      <c r="AD38" s="31"/>
-      <c r="AE38" s="31"/>
-      <c r="AF38" s="31"/>
+      <c r="AC38" s="32"/>
+      <c r="AD38" s="32"/>
+      <c r="AE38" s="32"/>
+      <c r="AF38" s="32"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
-        <v>477</v>
-      </c>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="33">
+      <c r="A39" s="31" t="s">
+        <v>478</v>
+      </c>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="34">
         <v>225.18</v>
       </c>
-      <c r="I39" s="32">
+      <c r="I39" s="33">
         <v>21.43</v>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="33">
         <v>22.28</v>
       </c>
-      <c r="K39" s="32">
+      <c r="K39" s="33">
         <v>18.3</v>
       </c>
-      <c r="L39" s="32">
+      <c r="L39" s="33">
         <v>10.55</v>
       </c>
-      <c r="M39" s="32">
+      <c r="M39" s="33">
         <v>6.42</v>
       </c>
-      <c r="N39" s="32">
+      <c r="N39" s="33">
         <v>6.02</v>
       </c>
-      <c r="O39" s="32">
+      <c r="O39" s="33">
         <v>5.48</v>
       </c>
-      <c r="P39" s="32">
+      <c r="P39" s="33">
         <v>5.7</v>
       </c>
-      <c r="Q39" s="32">
+      <c r="Q39" s="33">
         <v>6.24</v>
       </c>
-      <c r="R39" s="32">
+      <c r="R39" s="33">
         <v>5.89</v>
       </c>
-      <c r="S39" s="32">
+      <c r="S39" s="33">
         <v>4.84</v>
       </c>
-      <c r="T39" s="32">
+      <c r="T39" s="33">
         <v>4.6</v>
       </c>
-      <c r="U39" s="32">
+      <c r="U39" s="33">
         <v>4.66</v>
       </c>
-      <c r="V39" s="32">
+      <c r="V39" s="33">
         <v>5.08</v>
       </c>
-      <c r="W39" s="32">
+      <c r="W39" s="33">
         <v>5.93</v>
       </c>
-      <c r="X39" s="32">
+      <c r="X39" s="33">
         <v>6.63</v>
       </c>
-      <c r="Y39" s="31"/>
-      <c r="Z39" s="31"/>
-      <c r="AA39" s="31"/>
-      <c r="AB39" s="31"/>
-      <c r="AC39" s="31"/>
-      <c r="AD39" s="31"/>
-      <c r="AE39" s="31"/>
-      <c r="AF39" s="31"/>
+      <c r="Y39" s="32"/>
+      <c r="Z39" s="32"/>
+      <c r="AA39" s="32"/>
+      <c r="AB39" s="32"/>
+      <c r="AC39" s="32"/>
+      <c r="AD39" s="32"/>
+      <c r="AE39" s="32"/>
+      <c r="AF39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
-        <v>478</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
-      <c r="AA40" s="29"/>
-      <c r="AB40" s="29"/>
-      <c r="AC40" s="29"/>
-      <c r="AD40" s="29"/>
-      <c r="AE40" s="29"/>
-      <c r="AF40" s="29"/>
+      <c r="A40" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
+      <c r="AA40" s="30"/>
+      <c r="AB40" s="30"/>
+      <c r="AC40" s="30"/>
+      <c r="AD40" s="30"/>
+      <c r="AE40" s="30"/>
+      <c r="AF40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="30" t="s">
-        <v>479</v>
-      </c>
-      <c r="B41" s="32">
+      <c r="A41" s="31" t="s">
+        <v>480</v>
+      </c>
+      <c r="B41" s="33">
         <v>1.46</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="33">
         <v>1.5</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="33">
         <v>1.43</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="33">
         <v>1.3</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="33">
         <v>2.06</v>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="33">
         <v>2.35</v>
       </c>
-      <c r="H41" s="32">
+      <c r="H41" s="33">
         <v>2.97</v>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="33">
         <v>3.13</v>
       </c>
-      <c r="J41" s="32">
+      <c r="J41" s="33">
         <v>3.62</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="33">
         <v>3.62</v>
       </c>
-      <c r="L41" s="32">
+      <c r="L41" s="33">
         <v>3.17</v>
       </c>
-      <c r="M41" s="32">
+      <c r="M41" s="33">
         <v>1.79</v>
       </c>
-      <c r="N41" s="32">
+      <c r="N41" s="33">
         <v>1.76</v>
       </c>
-      <c r="O41" s="32">
+      <c r="O41" s="33">
         <v>1.1</v>
       </c>
-      <c r="P41" s="32">
+      <c r="P41" s="33">
         <v>1.32</v>
       </c>
-      <c r="Q41" s="32">
+      <c r="Q41" s="33">
         <v>1.41</v>
       </c>
-      <c r="R41" s="32">
+      <c r="R41" s="33">
         <v>1.35</v>
       </c>
-      <c r="S41" s="32">
+      <c r="S41" s="33">
         <v>1.87</v>
       </c>
-      <c r="T41" s="32">
+      <c r="T41" s="33">
         <v>2.53</v>
       </c>
-      <c r="U41" s="32">
+      <c r="U41" s="33">
         <v>3.59</v>
       </c>
-      <c r="V41" s="32">
+      <c r="V41" s="33">
         <v>3.27</v>
       </c>
-      <c r="W41" s="32">
+      <c r="W41" s="33">
         <v>2.9</v>
       </c>
-      <c r="X41" s="32">
+      <c r="X41" s="33">
         <v>2.3</v>
       </c>
-      <c r="Y41" s="32">
+      <c r="Y41" s="33">
         <v>4.62</v>
       </c>
-      <c r="Z41" s="32">
+      <c r="Z41" s="33">
         <v>6.55</v>
       </c>
-      <c r="AA41" s="32">
+      <c r="AA41" s="33">
         <v>8.08</v>
       </c>
-      <c r="AB41" s="32">
+      <c r="AB41" s="33">
         <v>4.2</v>
       </c>
-      <c r="AC41" s="31"/>
-      <c r="AD41" s="31"/>
-      <c r="AE41" s="31"/>
-      <c r="AF41" s="31"/>
+      <c r="AC41" s="32"/>
+      <c r="AD41" s="32"/>
+      <c r="AE41" s="32"/>
+      <c r="AF41" s="32"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
-        <v>480</v>
-      </c>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="32">
+      <c r="A42" s="31" t="s">
+        <v>481</v>
+      </c>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="33">
         <v>2.83</v>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="33">
         <v>3.13</v>
       </c>
-      <c r="H42" s="32">
+      <c r="H42" s="33">
         <v>3.3</v>
       </c>
-      <c r="I42" s="32">
+      <c r="I42" s="33">
         <v>3.11</v>
       </c>
-      <c r="J42" s="32">
+      <c r="J42" s="33">
         <v>2.84</v>
       </c>
-      <c r="K42" s="32">
+      <c r="K42" s="33">
         <v>2.3</v>
       </c>
-      <c r="L42" s="32">
+      <c r="L42" s="33">
         <v>1.82</v>
       </c>
-      <c r="M42" s="32">
+      <c r="M42" s="33">
         <v>1.47</v>
       </c>
-      <c r="N42" s="32">
+      <c r="N42" s="33">
         <v>1.39</v>
       </c>
-      <c r="O42" s="32">
+      <c r="O42" s="33">
         <v>1.39</v>
       </c>
-      <c r="P42" s="32">
+      <c r="P42" s="33">
         <v>1.64</v>
       </c>
-      <c r="Q42" s="32">
+      <c r="Q42" s="33">
         <v>2.0</v>
       </c>
-      <c r="R42" s="32">
+      <c r="R42" s="33">
         <v>2.36</v>
       </c>
-      <c r="S42" s="32">
+      <c r="S42" s="33">
         <v>2.75</v>
       </c>
-      <c r="T42" s="32">
+      <c r="T42" s="33">
         <v>2.9</v>
       </c>
-      <c r="U42" s="32">
+      <c r="U42" s="33">
         <v>3.33</v>
       </c>
-      <c r="V42" s="32">
+      <c r="V42" s="33">
         <v>3.8</v>
       </c>
-      <c r="W42" s="32">
+      <c r="W42" s="33">
         <v>4.49</v>
       </c>
-      <c r="X42" s="32">
+      <c r="X42" s="33">
         <v>4.88</v>
       </c>
-      <c r="Y42" s="31"/>
-      <c r="Z42" s="31"/>
-      <c r="AA42" s="31"/>
-      <c r="AB42" s="31"/>
-      <c r="AC42" s="31"/>
-      <c r="AD42" s="31"/>
-      <c r="AE42" s="31"/>
-      <c r="AF42" s="31"/>
+      <c r="Y42" s="32"/>
+      <c r="Z42" s="32"/>
+      <c r="AA42" s="32"/>
+      <c r="AB42" s="32"/>
+      <c r="AC42" s="32"/>
+      <c r="AD42" s="32"/>
+      <c r="AE42" s="32"/>
+      <c r="AF42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29"/>
-      <c r="Y43" s="29"/>
-      <c r="Z43" s="29"/>
-      <c r="AA43" s="29"/>
-      <c r="AB43" s="29"/>
-      <c r="AC43" s="29"/>
-      <c r="AD43" s="29"/>
-      <c r="AE43" s="29"/>
-      <c r="AF43" s="29"/>
+      <c r="A43" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
+      <c r="AA43" s="30"/>
+      <c r="AB43" s="30"/>
+      <c r="AC43" s="30"/>
+      <c r="AD43" s="30"/>
+      <c r="AE43" s="30"/>
+      <c r="AF43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
-        <v>482</v>
-      </c>
-      <c r="B44" s="32">
+      <c r="A44" s="31" t="s">
+        <v>483</v>
+      </c>
+      <c r="B44" s="33">
         <v>7.38</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <v>11.99</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="33">
         <v>7.96</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="33">
         <v>8.78</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="33">
         <v>20.21</v>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="33">
         <v>12.35</v>
       </c>
-      <c r="H44" s="32">
+      <c r="H44" s="33">
         <v>23.35</v>
       </c>
-      <c r="I44" s="32">
+      <c r="I44" s="33">
         <v>10.75</v>
       </c>
-      <c r="J44" s="32">
+      <c r="J44" s="33">
         <v>18.77</v>
       </c>
-      <c r="K44" s="32">
+      <c r="K44" s="33">
         <v>20.35</v>
       </c>
-      <c r="L44" s="31"/>
-      <c r="M44" s="33">
+      <c r="L44" s="32"/>
+      <c r="M44" s="34">
         <v>395.08</v>
       </c>
-      <c r="N44" s="32">
+      <c r="N44" s="33">
         <v>11.97</v>
       </c>
-      <c r="O44" s="32">
+      <c r="O44" s="33">
         <v>33.87</v>
       </c>
-      <c r="P44" s="32">
+      <c r="P44" s="33">
         <v>10.53</v>
       </c>
-      <c r="Q44" s="32">
+      <c r="Q44" s="33">
         <v>8.53</v>
       </c>
-      <c r="R44" s="32">
+      <c r="R44" s="33">
         <v>10.35</v>
       </c>
-      <c r="S44" s="32">
+      <c r="S44" s="33">
         <v>12.54</v>
       </c>
-      <c r="T44" s="32">
+      <c r="T44" s="33">
         <v>14.56</v>
       </c>
-      <c r="U44" s="32">
+      <c r="U44" s="33">
         <v>53.57</v>
       </c>
-      <c r="V44" s="32">
+      <c r="V44" s="33">
         <v>20.21</v>
       </c>
-      <c r="W44" s="32">
+      <c r="W44" s="33">
         <v>11.93</v>
       </c>
-      <c r="X44" s="32">
+      <c r="X44" s="33">
         <v>27.9</v>
       </c>
-      <c r="Y44" s="33">
+      <c r="Y44" s="34">
         <v>178.46</v>
       </c>
-      <c r="Z44" s="32">
+      <c r="Z44" s="33">
         <v>73.98</v>
       </c>
-      <c r="AA44" s="32">
+      <c r="AA44" s="33">
         <v>99.22</v>
       </c>
-      <c r="AB44" s="31"/>
-      <c r="AC44" s="31"/>
-      <c r="AD44" s="31"/>
-      <c r="AE44" s="31"/>
-      <c r="AF44" s="31"/>
+      <c r="AB44" s="32"/>
+      <c r="AC44" s="32"/>
+      <c r="AD44" s="32"/>
+      <c r="AE44" s="32"/>
+      <c r="AF44" s="32"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
-        <v>483</v>
-      </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="32">
+      <c r="A45" s="31" t="s">
+        <v>484</v>
+      </c>
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="33">
         <v>15.5</v>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="33">
         <v>15.85</v>
       </c>
-      <c r="H45" s="32">
+      <c r="H45" s="33">
         <v>25.36</v>
       </c>
-      <c r="I45" s="32">
+      <c r="I45" s="33">
         <v>28.49</v>
       </c>
-      <c r="J45" s="32">
+      <c r="J45" s="33">
         <v>38.35</v>
       </c>
-      <c r="K45" s="32">
+      <c r="K45" s="33">
         <v>60.61</v>
       </c>
-      <c r="L45" s="32">
+      <c r="L45" s="33">
         <v>65.85</v>
       </c>
-      <c r="M45" s="32">
+      <c r="M45" s="33">
         <v>15.09</v>
       </c>
-      <c r="N45" s="32">
+      <c r="N45" s="33">
         <v>11.56</v>
       </c>
-      <c r="O45" s="32">
+      <c r="O45" s="33">
         <v>11.65</v>
       </c>
-      <c r="P45" s="32">
+      <c r="P45" s="33">
         <v>11.11</v>
       </c>
-      <c r="Q45" s="32">
+      <c r="Q45" s="33">
         <v>14.14</v>
       </c>
-      <c r="R45" s="32">
+      <c r="R45" s="33">
         <v>17.11</v>
       </c>
-      <c r="S45" s="32">
+      <c r="S45" s="33">
         <v>17.34</v>
       </c>
-      <c r="T45" s="32">
+      <c r="T45" s="33">
         <v>19.77</v>
       </c>
-      <c r="U45" s="32">
+      <c r="U45" s="33">
         <v>28.74</v>
       </c>
-      <c r="V45" s="32">
+      <c r="V45" s="33">
         <v>31.19</v>
       </c>
-      <c r="W45" s="32">
+      <c r="W45" s="33">
         <v>41.6</v>
       </c>
-      <c r="X45" s="31"/>
-      <c r="Y45" s="31"/>
-      <c r="Z45" s="31"/>
-      <c r="AA45" s="31"/>
-      <c r="AB45" s="31"/>
-      <c r="AC45" s="31"/>
-      <c r="AD45" s="31"/>
-      <c r="AE45" s="31"/>
-      <c r="AF45" s="31"/>
+      <c r="X45" s="32"/>
+      <c r="Y45" s="32"/>
+      <c r="Z45" s="32"/>
+      <c r="AA45" s="32"/>
+      <c r="AB45" s="32"/>
+      <c r="AC45" s="32"/>
+      <c r="AD45" s="32"/>
+      <c r="AE45" s="32"/>
+      <c r="AF45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
-        <v>484</v>
-      </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29"/>
-      <c r="Y46" s="29"/>
-      <c r="Z46" s="29"/>
-      <c r="AA46" s="29"/>
-      <c r="AB46" s="29"/>
-      <c r="AC46" s="29"/>
-      <c r="AD46" s="29"/>
-      <c r="AE46" s="29"/>
-      <c r="AF46" s="29"/>
+      <c r="A46" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
+      <c r="AA46" s="30"/>
+      <c r="AB46" s="30"/>
+      <c r="AC46" s="30"/>
+      <c r="AD46" s="30"/>
+      <c r="AE46" s="30"/>
+      <c r="AF46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="30" t="s">
-        <v>485</v>
-      </c>
-      <c r="B47" s="32">
+      <c r="A47" s="31" t="s">
+        <v>486</v>
+      </c>
+      <c r="B47" s="33">
         <v>7.1</v>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="33">
         <v>5.95</v>
       </c>
-      <c r="D47" s="32">
+      <c r="D47" s="33">
         <v>6.64</v>
       </c>
-      <c r="E47" s="32">
+      <c r="E47" s="33">
         <v>6.39</v>
       </c>
-      <c r="F47" s="32">
+      <c r="F47" s="33">
         <v>11.18</v>
       </c>
-      <c r="G47" s="32">
+      <c r="G47" s="33">
         <v>11.77</v>
       </c>
-      <c r="H47" s="32">
+      <c r="H47" s="33">
         <v>12.7</v>
       </c>
-      <c r="I47" s="32">
+      <c r="I47" s="33">
         <v>11.31</v>
       </c>
-      <c r="J47" s="32">
+      <c r="J47" s="33">
         <v>16.09</v>
       </c>
-      <c r="K47" s="32">
+      <c r="K47" s="33">
         <v>22.19</v>
       </c>
-      <c r="L47" s="31"/>
-      <c r="M47" s="32">
+      <c r="L47" s="32"/>
+      <c r="M47" s="33">
         <v>22.36</v>
       </c>
-      <c r="N47" s="32">
+      <c r="N47" s="33">
         <v>12.7</v>
       </c>
-      <c r="O47" s="32">
+      <c r="O47" s="33">
         <v>7.92</v>
       </c>
-      <c r="P47" s="32">
+      <c r="P47" s="33">
         <v>6.02</v>
       </c>
-      <c r="Q47" s="32">
+      <c r="Q47" s="33">
         <v>7.42</v>
       </c>
-      <c r="R47" s="32">
+      <c r="R47" s="33">
         <v>8.04</v>
       </c>
-      <c r="S47" s="32">
+      <c r="S47" s="33">
         <v>10.18</v>
       </c>
-      <c r="T47" s="32">
+      <c r="T47" s="33">
         <v>10.12</v>
       </c>
-      <c r="U47" s="32">
+      <c r="U47" s="33">
         <v>31.85</v>
       </c>
-      <c r="V47" s="32">
+      <c r="V47" s="33">
         <v>19.02</v>
       </c>
-      <c r="W47" s="32">
+      <c r="W47" s="33">
         <v>12.23</v>
       </c>
-      <c r="X47" s="32">
+      <c r="X47" s="33">
         <v>11.81</v>
       </c>
-      <c r="Y47" s="32">
+      <c r="Y47" s="33">
         <v>26.2</v>
       </c>
-      <c r="Z47" s="32">
+      <c r="Z47" s="33">
         <v>30.58</v>
       </c>
-      <c r="AA47" s="32">
+      <c r="AA47" s="33">
         <v>38.66</v>
       </c>
-      <c r="AB47" s="32">
+      <c r="AB47" s="33">
         <v>20.91</v>
       </c>
-      <c r="AC47" s="31"/>
-      <c r="AD47" s="31"/>
-      <c r="AE47" s="31"/>
-      <c r="AF47" s="31"/>
+      <c r="AC47" s="32"/>
+      <c r="AD47" s="32"/>
+      <c r="AE47" s="32"/>
+      <c r="AF47" s="32"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="30" t="s">
-        <v>486</v>
-      </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="32">
+      <c r="A48" s="31" t="s">
+        <v>487</v>
+      </c>
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="33">
         <v>12.62</v>
       </c>
-      <c r="G48" s="32">
+      <c r="G48" s="33">
         <v>14.14</v>
       </c>
-      <c r="H48" s="32">
+      <c r="H48" s="33">
         <v>24.47</v>
       </c>
-      <c r="I48" s="32">
+      <c r="I48" s="33">
         <v>29.83</v>
       </c>
-      <c r="J48" s="32">
+      <c r="J48" s="33">
         <v>40.16</v>
       </c>
-      <c r="K48" s="32">
+      <c r="K48" s="33">
         <v>47.51</v>
       </c>
-      <c r="L48" s="32">
+      <c r="L48" s="33">
         <v>29.57</v>
       </c>
-      <c r="M48" s="32">
+      <c r="M48" s="33">
         <v>9.44</v>
       </c>
-      <c r="N48" s="32">
+      <c r="N48" s="33">
         <v>8.1</v>
       </c>
-      <c r="O48" s="32">
+      <c r="O48" s="33">
         <v>7.69</v>
       </c>
-      <c r="P48" s="32">
+      <c r="P48" s="33">
         <v>8.14</v>
       </c>
-      <c r="Q48" s="32">
+      <c r="Q48" s="33">
         <v>10.91</v>
       </c>
-      <c r="R48" s="32">
+      <c r="R48" s="33">
         <v>13.11</v>
       </c>
-      <c r="S48" s="32">
+      <c r="S48" s="33">
         <v>14.21</v>
       </c>
-      <c r="T48" s="32">
+      <c r="T48" s="33">
         <v>14.76</v>
       </c>
-      <c r="U48" s="32">
+      <c r="U48" s="33">
         <v>18.66</v>
       </c>
-      <c r="V48" s="32">
+      <c r="V48" s="33">
         <v>19.15</v>
       </c>
-      <c r="W48" s="32">
+      <c r="W48" s="33">
         <v>21.8</v>
       </c>
-      <c r="X48" s="32">
+      <c r="X48" s="33">
         <v>24.77</v>
       </c>
-      <c r="Y48" s="31"/>
-      <c r="Z48" s="31"/>
-      <c r="AA48" s="31"/>
-      <c r="AB48" s="31"/>
-      <c r="AC48" s="31"/>
-      <c r="AD48" s="31"/>
-      <c r="AE48" s="31"/>
-      <c r="AF48" s="31"/>
+      <c r="Y48" s="32"/>
+      <c r="Z48" s="32"/>
+      <c r="AA48" s="32"/>
+      <c r="AB48" s="32"/>
+      <c r="AC48" s="32"/>
+      <c r="AD48" s="32"/>
+      <c r="AE48" s="32"/>
+      <c r="AF48" s="32"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
-        <v>487</v>
-      </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
-      <c r="V49" s="29"/>
-      <c r="W49" s="29"/>
-      <c r="X49" s="29"/>
-      <c r="Y49" s="29"/>
-      <c r="Z49" s="29"/>
-      <c r="AA49" s="29"/>
-      <c r="AB49" s="29"/>
-      <c r="AC49" s="29"/>
-      <c r="AD49" s="29"/>
-      <c r="AE49" s="29"/>
-      <c r="AF49" s="29"/>
+      <c r="A49" s="29" t="s">
+        <v>488</v>
+      </c>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
+      <c r="AA49" s="30"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="30"/>
+      <c r="AD49" s="30"/>
+      <c r="AE49" s="30"/>
+      <c r="AF49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
-        <v>488</v>
-      </c>
-      <c r="B50" s="32">
+      <c r="A50" s="31" t="s">
+        <v>489</v>
+      </c>
+      <c r="B50" s="33">
         <v>11.25</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="33">
         <v>10.54</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="33">
         <v>12.44</v>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="33">
         <v>12.37</v>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="33">
         <v>25.45</v>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="33">
         <v>26.25</v>
       </c>
-      <c r="H50" s="32">
+      <c r="H50" s="33">
         <v>21.86</v>
       </c>
-      <c r="I50" s="32">
+      <c r="I50" s="33">
         <v>14.52</v>
       </c>
-      <c r="J50" s="32">
+      <c r="J50" s="33">
         <v>23.74</v>
       </c>
-      <c r="K50" s="32">
+      <c r="K50" s="33">
         <v>46.78</v>
       </c>
-      <c r="L50" s="31"/>
-      <c r="M50" s="31"/>
-      <c r="N50" s="32">
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
+      <c r="N50" s="33">
         <v>31.44</v>
       </c>
-      <c r="O50" s="32">
+      <c r="O50" s="33">
         <v>13.95</v>
       </c>
-      <c r="P50" s="32">
+      <c r="P50" s="33">
         <v>9.28</v>
       </c>
-      <c r="Q50" s="32">
+      <c r="Q50" s="33">
         <v>8.43</v>
       </c>
-      <c r="R50" s="32">
+      <c r="R50" s="33">
         <v>9.26</v>
       </c>
-      <c r="S50" s="32">
+      <c r="S50" s="33">
         <v>13.02</v>
       </c>
-      <c r="T50" s="32">
+      <c r="T50" s="33">
         <v>15.05</v>
       </c>
-      <c r="U50" s="32">
+      <c r="U50" s="33">
         <v>29.87</v>
       </c>
-      <c r="V50" s="32">
+      <c r="V50" s="33">
         <v>18.74</v>
       </c>
-      <c r="W50" s="32">
+      <c r="W50" s="33">
         <v>16.51</v>
       </c>
-      <c r="X50" s="32">
+      <c r="X50" s="33">
         <v>16.63</v>
       </c>
-      <c r="Y50" s="32">
+      <c r="Y50" s="33">
         <v>34.56</v>
       </c>
-      <c r="Z50" s="32">
+      <c r="Z50" s="33">
         <v>38.22</v>
       </c>
-      <c r="AA50" s="32">
+      <c r="AA50" s="33">
         <v>46.16</v>
       </c>
-      <c r="AB50" s="32">
+      <c r="AB50" s="33">
         <v>25.59</v>
       </c>
-      <c r="AC50" s="31"/>
-      <c r="AD50" s="31"/>
-      <c r="AE50" s="31"/>
-      <c r="AF50" s="31"/>
+      <c r="AC50" s="32"/>
+      <c r="AD50" s="32"/>
+      <c r="AE50" s="32"/>
+      <c r="AF50" s="32"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="30" t="s">
-        <v>489</v>
-      </c>
-      <c r="B51" s="31"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="32">
+      <c r="A51" s="31" t="s">
+        <v>490</v>
+      </c>
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="33">
         <v>20.83</v>
       </c>
-      <c r="G51" s="32">
+      <c r="G51" s="33">
         <v>23.03</v>
       </c>
-      <c r="H51" s="32">
+      <c r="H51" s="33">
         <v>63.4</v>
       </c>
-      <c r="I51" s="33">
+      <c r="I51" s="34">
         <v>133.88</v>
       </c>
-      <c r="J51" s="31"/>
-      <c r="K51" s="31"/>
-      <c r="L51" s="31"/>
-      <c r="M51" s="32">
+      <c r="J51" s="32"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="32"/>
+      <c r="M51" s="33">
         <v>16.5</v>
       </c>
-      <c r="N51" s="32">
+      <c r="N51" s="33">
         <v>11.82</v>
       </c>
-      <c r="O51" s="32">
+      <c r="O51" s="33">
         <v>10.27</v>
       </c>
-      <c r="P51" s="32">
+      <c r="P51" s="33">
         <v>10.69</v>
       </c>
-      <c r="Q51" s="32">
+      <c r="Q51" s="33">
         <v>13.24</v>
       </c>
-      <c r="R51" s="32">
+      <c r="R51" s="33">
         <v>15.71</v>
       </c>
-      <c r="S51" s="32">
+      <c r="S51" s="33">
         <v>17.65</v>
       </c>
-      <c r="T51" s="32">
+      <c r="T51" s="33">
         <v>18.6</v>
       </c>
-      <c r="U51" s="32">
+      <c r="U51" s="33">
         <v>22.47</v>
       </c>
-      <c r="V51" s="32">
+      <c r="V51" s="33">
         <v>24.06</v>
       </c>
-      <c r="W51" s="32">
+      <c r="W51" s="33">
         <v>28.63</v>
       </c>
-      <c r="X51" s="32">
+      <c r="X51" s="33">
         <v>31.99</v>
       </c>
-      <c r="Y51" s="31"/>
-      <c r="Z51" s="31"/>
-      <c r="AA51" s="31"/>
-      <c r="AB51" s="31"/>
-      <c r="AC51" s="31"/>
-      <c r="AD51" s="31"/>
-      <c r="AE51" s="31"/>
-      <c r="AF51" s="31"/>
+      <c r="Y51" s="32"/>
+      <c r="Z51" s="32"/>
+      <c r="AA51" s="32"/>
+      <c r="AB51" s="32"/>
+      <c r="AC51" s="32"/>
+      <c r="AD51" s="32"/>
+      <c r="AE51" s="32"/>
+      <c r="AF51" s="32"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="28" t="s">
-        <v>490</v>
-      </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="29"/>
-      <c r="S52" s="29"/>
-      <c r="T52" s="29"/>
-      <c r="U52" s="29"/>
-      <c r="V52" s="29"/>
-      <c r="W52" s="29"/>
-      <c r="X52" s="29"/>
-      <c r="Y52" s="29"/>
-      <c r="Z52" s="29"/>
-      <c r="AA52" s="29"/>
-      <c r="AB52" s="29"/>
-      <c r="AC52" s="29"/>
-      <c r="AD52" s="29"/>
-      <c r="AE52" s="29"/>
-      <c r="AF52" s="29"/>
+      <c r="A52" s="29" t="s">
+        <v>491</v>
+      </c>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="30"/>
+      <c r="X52" s="30"/>
+      <c r="Y52" s="30"/>
+      <c r="Z52" s="30"/>
+      <c r="AA52" s="30"/>
+      <c r="AB52" s="30"/>
+      <c r="AC52" s="30"/>
+      <c r="AD52" s="30"/>
+      <c r="AE52" s="30"/>
+      <c r="AF52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
-        <v>491</v>
-      </c>
-      <c r="B53" s="32">
+      <c r="A53" s="31" t="s">
+        <v>492</v>
+      </c>
+      <c r="B53" s="33">
         <v>7.84</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="33">
         <v>8.51</v>
       </c>
-      <c r="D53" s="32">
+      <c r="D53" s="33">
         <v>10.35</v>
       </c>
-      <c r="E53" s="32">
+      <c r="E53" s="33">
         <v>12.52</v>
       </c>
-      <c r="F53" s="32">
+      <c r="F53" s="33">
         <v>20.81</v>
       </c>
-      <c r="G53" s="32">
+      <c r="G53" s="33">
         <v>17.03</v>
       </c>
-      <c r="H53" s="32">
+      <c r="H53" s="33">
         <v>17.84</v>
       </c>
-      <c r="I53" s="32">
+      <c r="I53" s="33">
         <v>13.9</v>
       </c>
-      <c r="J53" s="32">
+      <c r="J53" s="33">
         <v>23.55</v>
       </c>
-      <c r="K53" s="32">
+      <c r="K53" s="33">
         <v>46.32</v>
       </c>
-      <c r="L53" s="33">
+      <c r="L53" s="34">
         <v>2202.26</v>
       </c>
-      <c r="M53" s="33">
+      <c r="M53" s="34">
         <v>301.25</v>
       </c>
-      <c r="N53" s="32">
+      <c r="N53" s="33">
         <v>30.3</v>
       </c>
-      <c r="O53" s="32">
+      <c r="O53" s="33">
         <v>13.95</v>
       </c>
-      <c r="P53" s="32">
+      <c r="P53" s="33">
         <v>9.28</v>
       </c>
-      <c r="Q53" s="32">
+      <c r="Q53" s="33">
         <v>13.04</v>
       </c>
-      <c r="R53" s="32">
+      <c r="R53" s="33">
         <v>12.96</v>
       </c>
-      <c r="S53" s="32">
+      <c r="S53" s="33">
         <v>20.72</v>
       </c>
-      <c r="T53" s="32">
+      <c r="T53" s="33">
         <v>15.05</v>
       </c>
-      <c r="U53" s="32">
+      <c r="U53" s="33">
         <v>68.27</v>
       </c>
-      <c r="V53" s="32">
+      <c r="V53" s="33">
         <v>28.67</v>
       </c>
-      <c r="W53" s="32">
+      <c r="W53" s="33">
         <v>17.34</v>
       </c>
-      <c r="X53" s="32">
+      <c r="X53" s="33">
         <v>18.58</v>
       </c>
-      <c r="Y53" s="32">
+      <c r="Y53" s="33">
         <v>38.66</v>
       </c>
-      <c r="Z53" s="32">
+      <c r="Z53" s="33">
         <v>39.22</v>
       </c>
-      <c r="AA53" s="32">
+      <c r="AA53" s="33">
         <v>46.16</v>
       </c>
-      <c r="AB53" s="32">
+      <c r="AB53" s="33">
         <v>25.59</v>
       </c>
-      <c r="AC53" s="31"/>
-      <c r="AD53" s="31"/>
-      <c r="AE53" s="31"/>
-      <c r="AF53" s="31"/>
+      <c r="AC53" s="32"/>
+      <c r="AD53" s="32"/>
+      <c r="AE53" s="32"/>
+      <c r="AF53" s="32"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="30" t="s">
-        <v>492</v>
-      </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="32">
+      <c r="A54" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="33">
         <v>3.12</v>
       </c>
-      <c r="G54" s="32">
+      <c r="G54" s="33">
         <v>3.84</v>
       </c>
-      <c r="H54" s="32">
+      <c r="H54" s="33">
         <v>4.43</v>
       </c>
-      <c r="I54" s="32">
+      <c r="I54" s="33">
         <v>4.22</v>
       </c>
-      <c r="J54" s="32">
+      <c r="J54" s="33">
         <v>3.75</v>
       </c>
-      <c r="K54" s="32">
+      <c r="K54" s="33">
         <v>2.9</v>
       </c>
-      <c r="L54" s="32">
+      <c r="L54" s="33">
         <v>2.18</v>
       </c>
-      <c r="M54" s="32">
+      <c r="M54" s="33">
         <v>1.7</v>
       </c>
-      <c r="N54" s="32">
+      <c r="N54" s="33">
         <v>1.75</v>
       </c>
-      <c r="O54" s="32">
+      <c r="O54" s="33">
         <v>1.84</v>
       </c>
-      <c r="P54" s="32">
+      <c r="P54" s="33">
         <v>2.31</v>
       </c>
-      <c r="Q54" s="32">
+      <c r="Q54" s="33">
         <v>2.9</v>
       </c>
-      <c r="R54" s="32">
+      <c r="R54" s="33">
         <v>3.39</v>
       </c>
-      <c r="S54" s="32">
+      <c r="S54" s="33">
         <v>3.75</v>
       </c>
-      <c r="T54" s="32">
+      <c r="T54" s="33">
         <v>3.87</v>
       </c>
-      <c r="U54" s="32">
+      <c r="U54" s="33">
         <v>4.45</v>
       </c>
-      <c r="V54" s="32">
+      <c r="V54" s="33">
         <v>5.23</v>
       </c>
-      <c r="W54" s="32">
+      <c r="W54" s="33">
         <v>6.48</v>
       </c>
-      <c r="X54" s="32">
+      <c r="X54" s="33">
         <v>7.37</v>
       </c>
-      <c r="Y54" s="31"/>
-      <c r="Z54" s="31"/>
-      <c r="AA54" s="31"/>
-      <c r="AB54" s="31"/>
-      <c r="AC54" s="31"/>
-      <c r="AD54" s="31"/>
-      <c r="AE54" s="31"/>
-      <c r="AF54" s="31"/>
+      <c r="Y54" s="32"/>
+      <c r="Z54" s="32"/>
+      <c r="AA54" s="32"/>
+      <c r="AB54" s="32"/>
+      <c r="AC54" s="32"/>
+      <c r="AD54" s="32"/>
+      <c r="AE54" s="32"/>
+      <c r="AF54" s="32"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
-        <v>493</v>
-      </c>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="29"/>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
-      <c r="Q55" s="29"/>
-      <c r="R55" s="29"/>
-      <c r="S55" s="29"/>
-      <c r="T55" s="29"/>
-      <c r="U55" s="29"/>
-      <c r="V55" s="29"/>
-      <c r="W55" s="29"/>
-      <c r="X55" s="29"/>
-      <c r="Y55" s="29"/>
-      <c r="Z55" s="29"/>
-      <c r="AA55" s="29"/>
-      <c r="AB55" s="29"/>
-      <c r="AC55" s="29"/>
-      <c r="AD55" s="29"/>
-      <c r="AE55" s="29"/>
-      <c r="AF55" s="29"/>
+      <c r="A55" s="29" t="s">
+        <v>494</v>
+      </c>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="30"/>
+      <c r="X55" s="30"/>
+      <c r="Y55" s="30"/>
+      <c r="Z55" s="30"/>
+      <c r="AA55" s="30"/>
+      <c r="AB55" s="30"/>
+      <c r="AC55" s="30"/>
+      <c r="AD55" s="30"/>
+      <c r="AE55" s="30"/>
+      <c r="AF55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
-        <v>494</v>
-      </c>
-      <c r="B56" s="32">
+      <c r="A56" s="31" t="s">
+        <v>495</v>
+      </c>
+      <c r="B56" s="33">
         <v>7.53</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="33">
         <v>0.28</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="33">
         <v>0.63</v>
       </c>
-      <c r="E56" s="36">
+      <c r="E56" s="37">
         <v>-0.17</v>
       </c>
-      <c r="F56" s="36">
+      <c r="F56" s="37">
         <v>-1.53</v>
       </c>
-      <c r="G56" s="36">
+      <c r="G56" s="37">
         <v>-0.83</v>
       </c>
-      <c r="H56" s="36">
+      <c r="H56" s="37">
         <v>-0.54</v>
       </c>
-      <c r="I56" s="32">
+      <c r="I56" s="33">
         <v>0.3</v>
       </c>
-      <c r="J56" s="32">
+      <c r="J56" s="33">
         <v>0.2</v>
       </c>
-      <c r="K56" s="32">
+      <c r="K56" s="33">
         <v>0.39</v>
       </c>
-      <c r="L56" s="31"/>
-      <c r="M56" s="31"/>
-      <c r="N56" s="36">
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+      <c r="N56" s="37">
         <v>-1.18</v>
       </c>
-      <c r="O56" s="36">
+      <c r="O56" s="37">
         <v>-0.29</v>
       </c>
-      <c r="P56" s="36">
+      <c r="P56" s="37">
         <v>-1.25</v>
       </c>
-      <c r="Q56" s="32">
+      <c r="Q56" s="33">
         <v>0.37</v>
       </c>
-      <c r="R56" s="32">
+      <c r="R56" s="33">
         <v>0.44</v>
       </c>
-      <c r="S56" s="36">
+      <c r="S56" s="37">
         <v>-1.65</v>
       </c>
-      <c r="T56" s="32">
+      <c r="T56" s="33">
         <v>0.2</v>
       </c>
-      <c r="U56" s="36">
+      <c r="U56" s="37">
         <v>-1.19</v>
       </c>
-      <c r="V56" s="36">
+      <c r="V56" s="37">
         <v>-3.25</v>
       </c>
-      <c r="W56" s="32">
+      <c r="W56" s="33">
         <v>0.65</v>
       </c>
-      <c r="X56" s="32">
+      <c r="X56" s="33">
         <v>2.0</v>
       </c>
-      <c r="Y56" s="36">
+      <c r="Y56" s="37">
         <v>-10.46</v>
       </c>
-      <c r="Z56" s="32">
+      <c r="Z56" s="33">
         <v>1.15</v>
       </c>
-      <c r="AA56" s="32">
+      <c r="AA56" s="33">
         <v>0.99</v>
       </c>
-      <c r="AB56" s="32">
+      <c r="AB56" s="33">
         <v>0.23</v>
       </c>
-      <c r="AC56" s="31"/>
-      <c r="AD56" s="31"/>
-      <c r="AE56" s="31"/>
-      <c r="AF56" s="31"/>
+      <c r="AC56" s="32"/>
+      <c r="AD56" s="32"/>
+      <c r="AE56" s="32"/>
+      <c r="AF56" s="32"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="30" t="s">
-        <v>495</v>
-      </c>
-      <c r="B57" s="31"/>
-      <c r="C57" s="31"/>
-      <c r="D57" s="31"/>
-      <c r="E57" s="31"/>
-      <c r="F57" s="32">
+      <c r="A57" s="31" t="s">
+        <v>496</v>
+      </c>
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="33">
         <v>13.39</v>
       </c>
-      <c r="G57" s="31"/>
-      <c r="H57" s="31"/>
-      <c r="I57" s="32">
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="33">
         <v>3.81</v>
       </c>
-      <c r="J57" s="31"/>
-      <c r="K57" s="31"/>
-      <c r="L57" s="31"/>
-      <c r="M57" s="31"/>
-      <c r="N57" s="36">
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
+      <c r="L57" s="32"/>
+      <c r="M57" s="32"/>
+      <c r="N57" s="37">
         <v>-0.95</v>
       </c>
-      <c r="O57" s="36">
+      <c r="O57" s="37">
         <v>-1.24</v>
       </c>
-      <c r="P57" s="32">
+      <c r="P57" s="33">
         <v>0.61</v>
       </c>
-      <c r="Q57" s="32">
+      <c r="Q57" s="33">
         <v>1.06</v>
       </c>
-      <c r="R57" s="32">
+      <c r="R57" s="33">
         <v>2.34</v>
       </c>
-      <c r="S57" s="32">
+      <c r="S57" s="33">
         <v>2.36</v>
       </c>
-      <c r="T57" s="32">
+      <c r="T57" s="33">
         <v>1.69</v>
       </c>
-      <c r="U57" s="36">
+      <c r="U57" s="37">
         <v>-14.88</v>
       </c>
-      <c r="V57" s="32">
+      <c r="V57" s="33">
         <v>2.29</v>
       </c>
-      <c r="W57" s="32">
+      <c r="W57" s="33">
         <v>1.38</v>
       </c>
-      <c r="X57" s="32">
+      <c r="X57" s="33">
         <v>0.93</v>
       </c>
-      <c r="Y57" s="31"/>
-      <c r="Z57" s="31"/>
-      <c r="AA57" s="31"/>
-      <c r="AB57" s="31"/>
-      <c r="AC57" s="31"/>
-      <c r="AD57" s="31"/>
-      <c r="AE57" s="31"/>
-      <c r="AF57" s="31"/>
+      <c r="Y57" s="32"/>
+      <c r="Z57" s="32"/>
+      <c r="AA57" s="32"/>
+      <c r="AB57" s="32"/>
+      <c r="AC57" s="32"/>
+      <c r="AD57" s="32"/>
+      <c r="AE57" s="32"/>
+      <c r="AF57" s="32"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
-        <v>496</v>
-      </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
-      <c r="M58" s="29"/>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
-      <c r="Q58" s="29"/>
-      <c r="R58" s="29"/>
-      <c r="S58" s="29"/>
-      <c r="T58" s="29"/>
-      <c r="U58" s="29"/>
-      <c r="V58" s="29"/>
-      <c r="W58" s="29"/>
-      <c r="X58" s="29"/>
-      <c r="Y58" s="29"/>
-      <c r="Z58" s="29"/>
-      <c r="AA58" s="29"/>
-      <c r="AB58" s="29"/>
-      <c r="AC58" s="29"/>
-      <c r="AD58" s="29"/>
-      <c r="AE58" s="29"/>
-      <c r="AF58" s="29"/>
+      <c r="A58" s="29" t="s">
+        <v>497</v>
+      </c>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="30"/>
+      <c r="X58" s="30"/>
+      <c r="Y58" s="30"/>
+      <c r="Z58" s="30"/>
+      <c r="AA58" s="30"/>
+      <c r="AB58" s="30"/>
+      <c r="AC58" s="30"/>
+      <c r="AD58" s="30"/>
+      <c r="AE58" s="30"/>
+      <c r="AF58" s="30"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="30" t="s">
-        <v>497</v>
-      </c>
-      <c r="B59" s="32">
+      <c r="A59" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B59" s="33">
         <v>2.02</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="33">
         <v>2.34</v>
       </c>
-      <c r="D59" s="32">
+      <c r="D59" s="33">
         <v>1.55</v>
       </c>
-      <c r="E59" s="32">
+      <c r="E59" s="33">
         <v>1.51</v>
       </c>
-      <c r="F59" s="32">
+      <c r="F59" s="33">
         <v>2.25</v>
       </c>
-      <c r="G59" s="32">
+      <c r="G59" s="33">
         <v>2.58</v>
       </c>
-      <c r="H59" s="32">
+      <c r="H59" s="33">
         <v>3.36</v>
       </c>
-      <c r="I59" s="32">
+      <c r="I59" s="33">
         <v>2.77</v>
       </c>
-      <c r="J59" s="32">
+      <c r="J59" s="33">
         <v>3.43</v>
       </c>
-      <c r="K59" s="32">
+      <c r="K59" s="33">
         <v>3.61</v>
       </c>
-      <c r="L59" s="32">
+      <c r="L59" s="33">
         <v>3.34</v>
       </c>
-      <c r="M59" s="32">
+      <c r="M59" s="33">
         <v>1.77</v>
       </c>
-      <c r="N59" s="32">
+      <c r="N59" s="33">
         <v>1.52</v>
       </c>
-      <c r="O59" s="32">
+      <c r="O59" s="33">
         <v>0.97</v>
       </c>
-      <c r="P59" s="32">
+      <c r="P59" s="33">
         <v>1.2</v>
       </c>
-      <c r="Q59" s="32">
+      <c r="Q59" s="33">
         <v>1.38</v>
       </c>
-      <c r="R59" s="32">
+      <c r="R59" s="33">
         <v>1.46</v>
       </c>
-      <c r="S59" s="32">
+      <c r="S59" s="33">
         <v>1.7</v>
       </c>
-      <c r="T59" s="32">
+      <c r="T59" s="33">
         <v>2.43</v>
       </c>
-      <c r="U59" s="32">
+      <c r="U59" s="33">
         <v>3.49</v>
       </c>
-      <c r="V59" s="32">
+      <c r="V59" s="33">
         <v>3.02</v>
       </c>
-      <c r="W59" s="32">
+      <c r="W59" s="33">
         <v>2.68</v>
       </c>
-      <c r="X59" s="32">
+      <c r="X59" s="33">
         <v>2.23</v>
       </c>
-      <c r="Y59" s="32">
+      <c r="Y59" s="33">
         <v>4.57</v>
       </c>
-      <c r="Z59" s="32">
+      <c r="Z59" s="33">
         <v>6.43</v>
       </c>
-      <c r="AA59" s="32">
+      <c r="AA59" s="33">
         <v>7.83</v>
       </c>
-      <c r="AB59" s="32">
+      <c r="AB59" s="33">
         <v>3.96</v>
       </c>
-      <c r="AC59" s="31"/>
-      <c r="AD59" s="31"/>
-      <c r="AE59" s="31"/>
-      <c r="AF59" s="31"/>
+      <c r="AC59" s="32"/>
+      <c r="AD59" s="32"/>
+      <c r="AE59" s="32"/>
+      <c r="AF59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="30" t="s">
-        <v>498</v>
-      </c>
-      <c r="B60" s="32">
+      <c r="A60" s="31" t="s">
+        <v>499</v>
+      </c>
+      <c r="B60" s="33">
         <v>1.94</v>
       </c>
-      <c r="C60" s="32">
+      <c r="C60" s="33">
         <v>2.04</v>
       </c>
-      <c r="D60" s="32">
+      <c r="D60" s="33">
         <v>2.22</v>
       </c>
-      <c r="E60" s="32">
+      <c r="E60" s="33">
         <v>2.49</v>
       </c>
-      <c r="F60" s="32">
+      <c r="F60" s="33">
         <v>2.88</v>
       </c>
-      <c r="G60" s="32">
+      <c r="G60" s="33">
         <v>3.13</v>
       </c>
-      <c r="H60" s="32">
+      <c r="H60" s="33">
         <v>3.29</v>
       </c>
-      <c r="I60" s="32">
+      <c r="I60" s="33">
         <v>3.01</v>
       </c>
-      <c r="J60" s="32">
+      <c r="J60" s="33">
         <v>2.77</v>
       </c>
-      <c r="K60" s="32">
+      <c r="K60" s="33">
         <v>2.26</v>
       </c>
-      <c r="L60" s="32">
+      <c r="L60" s="33">
         <v>1.74</v>
       </c>
-      <c r="M60" s="32">
+      <c r="M60" s="33">
         <v>1.36</v>
       </c>
-      <c r="N60" s="32">
+      <c r="N60" s="33">
         <v>1.3</v>
       </c>
-      <c r="O60" s="32">
+      <c r="O60" s="33">
         <v>1.32</v>
       </c>
-      <c r="P60" s="32">
+      <c r="P60" s="33">
         <v>1.58</v>
       </c>
-      <c r="Q60" s="32">
+      <c r="Q60" s="33">
         <v>1.98</v>
       </c>
-      <c r="R60" s="32">
+      <c r="R60" s="33">
         <v>2.31</v>
       </c>
-      <c r="S60" s="32">
+      <c r="S60" s="33">
         <v>2.61</v>
       </c>
-      <c r="T60" s="32">
+      <c r="T60" s="33">
         <v>2.75</v>
       </c>
-      <c r="U60" s="32">
+      <c r="U60" s="33">
         <v>3.19</v>
       </c>
-      <c r="V60" s="32">
+      <c r="V60" s="33">
         <v>3.67</v>
       </c>
-      <c r="W60" s="32">
+      <c r="W60" s="33">
         <v>4.36</v>
       </c>
-      <c r="X60" s="32">
+      <c r="X60" s="33">
         <v>4.76</v>
       </c>
-      <c r="Y60" s="31"/>
-      <c r="Z60" s="31"/>
-      <c r="AA60" s="31"/>
-      <c r="AB60" s="31"/>
-      <c r="AC60" s="31"/>
-      <c r="AD60" s="31"/>
-      <c r="AE60" s="31"/>
-      <c r="AF60" s="31"/>
+      <c r="Y60" s="32"/>
+      <c r="Z60" s="32"/>
+      <c r="AA60" s="32"/>
+      <c r="AB60" s="32"/>
+      <c r="AC60" s="32"/>
+      <c r="AD60" s="32"/>
+      <c r="AE60" s="32"/>
+      <c r="AF60" s="32"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
-        <v>499</v>
-      </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
-      <c r="R61" s="29"/>
-      <c r="S61" s="29"/>
-      <c r="T61" s="29"/>
-      <c r="U61" s="29"/>
-      <c r="V61" s="29"/>
-      <c r="W61" s="29"/>
-      <c r="X61" s="29"/>
-      <c r="Y61" s="29"/>
-      <c r="Z61" s="29"/>
-      <c r="AA61" s="29"/>
-      <c r="AB61" s="29"/>
-      <c r="AC61" s="29"/>
-      <c r="AD61" s="29"/>
-      <c r="AE61" s="29"/>
-      <c r="AF61" s="29"/>
+      <c r="A61" s="29" t="s">
+        <v>500</v>
+      </c>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="30"/>
+      <c r="X61" s="30"/>
+      <c r="Y61" s="30"/>
+      <c r="Z61" s="30"/>
+      <c r="AA61" s="30"/>
+      <c r="AB61" s="30"/>
+      <c r="AC61" s="30"/>
+      <c r="AD61" s="30"/>
+      <c r="AE61" s="30"/>
+      <c r="AF61" s="30"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="30" t="s">
-        <v>500</v>
-      </c>
-      <c r="B62" s="32">
+      <c r="A62" s="31" t="s">
+        <v>501</v>
+      </c>
+      <c r="B62" s="33">
         <v>5.84</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="33">
         <v>7.5</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="33">
         <v>5.49</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="33">
         <v>5.84</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="33">
         <v>9.33</v>
       </c>
-      <c r="G62" s="32">
+      <c r="G62" s="33">
         <v>9.35</v>
       </c>
-      <c r="H62" s="32">
+      <c r="H62" s="33">
         <v>10.73</v>
       </c>
-      <c r="I62" s="32">
+      <c r="I62" s="33">
         <v>7.79</v>
       </c>
-      <c r="J62" s="32">
+      <c r="J62" s="33">
         <v>10.44</v>
       </c>
-      <c r="K62" s="32">
+      <c r="K62" s="33">
         <v>15.54</v>
       </c>
-      <c r="L62" s="33">
+      <c r="L62" s="34">
         <v>153.61</v>
       </c>
-      <c r="M62" s="32">
+      <c r="M62" s="33">
         <v>15.33</v>
       </c>
-      <c r="N62" s="32">
+      <c r="N62" s="33">
         <v>7.46</v>
       </c>
-      <c r="O62" s="32">
+      <c r="O62" s="33">
         <v>5.5</v>
       </c>
-      <c r="P62" s="32">
+      <c r="P62" s="33">
         <v>4.14</v>
       </c>
-      <c r="Q62" s="32">
+      <c r="Q62" s="33">
         <v>4.4</v>
       </c>
-      <c r="R62" s="32">
+      <c r="R62" s="33">
         <v>5.38</v>
       </c>
-      <c r="S62" s="32">
+      <c r="S62" s="33">
         <v>5.76</v>
       </c>
-      <c r="T62" s="32">
+      <c r="T62" s="33">
         <v>7.55</v>
       </c>
-      <c r="U62" s="32">
+      <c r="U62" s="33">
         <v>13.46</v>
       </c>
-      <c r="V62" s="32">
+      <c r="V62" s="33">
         <v>10.16</v>
       </c>
-      <c r="W62" s="32">
+      <c r="W62" s="33">
         <v>8.24</v>
       </c>
-      <c r="X62" s="32">
+      <c r="X62" s="33">
         <v>8.2</v>
       </c>
-      <c r="Y62" s="32">
+      <c r="Y62" s="33">
         <v>14.88</v>
       </c>
-      <c r="Z62" s="32">
+      <c r="Z62" s="33">
         <v>21.21</v>
       </c>
-      <c r="AA62" s="32">
+      <c r="AA62" s="33">
         <v>34.69</v>
       </c>
-      <c r="AB62" s="32">
+      <c r="AB62" s="33">
         <v>19.49</v>
       </c>
-      <c r="AC62" s="31"/>
-      <c r="AD62" s="31"/>
-      <c r="AE62" s="31"/>
-      <c r="AF62" s="31"/>
+      <c r="AC62" s="32"/>
+      <c r="AD62" s="32"/>
+      <c r="AE62" s="32"/>
+      <c r="AF62" s="32"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="30" t="s">
-        <v>501</v>
-      </c>
-      <c r="B63" s="32">
+      <c r="A63" s="31" t="s">
+        <v>502</v>
+      </c>
+      <c r="B63" s="33">
         <v>6.62</v>
       </c>
-      <c r="C63" s="32">
+      <c r="C63" s="33">
         <v>7.39</v>
       </c>
-      <c r="D63" s="32">
+      <c r="D63" s="33">
         <v>8.08</v>
       </c>
-      <c r="E63" s="32">
+      <c r="E63" s="33">
         <v>8.59</v>
       </c>
-      <c r="F63" s="32">
+      <c r="F63" s="33">
         <v>9.48</v>
       </c>
-      <c r="G63" s="32">
+      <c r="G63" s="33">
         <v>10.35</v>
       </c>
-      <c r="H63" s="32">
+      <c r="H63" s="33">
         <v>12.7</v>
       </c>
-      <c r="I63" s="32">
+      <c r="I63" s="33">
         <v>13.53</v>
       </c>
-      <c r="J63" s="32">
+      <c r="J63" s="33">
         <v>14.8</v>
       </c>
-      <c r="K63" s="32">
+      <c r="K63" s="33">
         <v>14.83</v>
       </c>
-      <c r="L63" s="32">
+      <c r="L63" s="33">
         <v>10.57</v>
       </c>
-      <c r="M63" s="32">
+      <c r="M63" s="33">
         <v>6.1</v>
       </c>
-      <c r="N63" s="32">
+      <c r="N63" s="33">
         <v>5.19</v>
       </c>
-      <c r="O63" s="32">
+      <c r="O63" s="33">
         <v>4.92</v>
       </c>
-      <c r="P63" s="32">
+      <c r="P63" s="33">
         <v>5.32</v>
       </c>
-      <c r="Q63" s="32">
+      <c r="Q63" s="33">
         <v>6.72</v>
       </c>
-      <c r="R63" s="32">
+      <c r="R63" s="33">
         <v>7.99</v>
       </c>
-      <c r="S63" s="32">
+      <c r="S63" s="33">
         <v>8.68</v>
       </c>
-      <c r="T63" s="32">
+      <c r="T63" s="33">
         <v>9.27</v>
       </c>
-      <c r="U63" s="32">
+      <c r="U63" s="33">
         <v>10.9</v>
       </c>
-      <c r="V63" s="32">
+      <c r="V63" s="33">
         <v>12.19</v>
       </c>
-      <c r="W63" s="32">
+      <c r="W63" s="33">
         <v>14.94</v>
       </c>
-      <c r="X63" s="32">
+      <c r="X63" s="33">
         <v>17.44</v>
       </c>
-      <c r="Y63" s="31"/>
-      <c r="Z63" s="31"/>
-      <c r="AA63" s="31"/>
-      <c r="AB63" s="31"/>
-      <c r="AC63" s="31"/>
-      <c r="AD63" s="31"/>
-      <c r="AE63" s="31"/>
-      <c r="AF63" s="31"/>
+      <c r="Y63" s="32"/>
+      <c r="Z63" s="32"/>
+      <c r="AA63" s="32"/>
+      <c r="AB63" s="32"/>
+      <c r="AC63" s="32"/>
+      <c r="AD63" s="32"/>
+      <c r="AE63" s="32"/>
+      <c r="AF63" s="32"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
-        <v>502</v>
-      </c>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
-      <c r="O64" s="29"/>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="29"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="29"/>
-      <c r="T64" s="29"/>
-      <c r="U64" s="29"/>
-      <c r="V64" s="29"/>
-      <c r="W64" s="29"/>
-      <c r="X64" s="29"/>
-      <c r="Y64" s="29"/>
-      <c r="Z64" s="29"/>
-      <c r="AA64" s="29"/>
-      <c r="AB64" s="29"/>
-      <c r="AC64" s="29"/>
-      <c r="AD64" s="29"/>
-      <c r="AE64" s="29"/>
-      <c r="AF64" s="29"/>
+      <c r="A64" s="29" t="s">
+        <v>503</v>
+      </c>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="30"/>
+      <c r="S64" s="30"/>
+      <c r="T64" s="30"/>
+      <c r="U64" s="30"/>
+      <c r="V64" s="30"/>
+      <c r="W64" s="30"/>
+      <c r="X64" s="30"/>
+      <c r="Y64" s="30"/>
+      <c r="Z64" s="30"/>
+      <c r="AA64" s="30"/>
+      <c r="AB64" s="30"/>
+      <c r="AC64" s="30"/>
+      <c r="AD64" s="30"/>
+      <c r="AE64" s="30"/>
+      <c r="AF64" s="30"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B65" s="32">
+      <c r="A65" s="31" t="s">
+        <v>504</v>
+      </c>
+      <c r="B65" s="33">
         <v>9.09</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="33">
         <v>15.51</v>
       </c>
-      <c r="D65" s="32">
+      <c r="D65" s="33">
         <v>7.59</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="33">
         <v>7.83</v>
       </c>
-      <c r="F65" s="32">
+      <c r="F65" s="33">
         <v>16.14</v>
       </c>
-      <c r="G65" s="32">
+      <c r="G65" s="33">
         <v>11.87</v>
       </c>
-      <c r="H65" s="32">
+      <c r="H65" s="33">
         <v>21.93</v>
       </c>
-      <c r="I65" s="32">
+      <c r="I65" s="33">
         <v>8.4</v>
       </c>
-      <c r="J65" s="32">
+      <c r="J65" s="33">
         <v>14.61</v>
       </c>
-      <c r="K65" s="32">
+      <c r="K65" s="33">
         <v>18.06</v>
       </c>
-      <c r="L65" s="33">
+      <c r="L65" s="34">
         <v>247.18</v>
       </c>
-      <c r="M65" s="32">
+      <c r="M65" s="33">
         <v>14.78</v>
       </c>
-      <c r="N65" s="32">
+      <c r="N65" s="33">
         <v>6.16</v>
       </c>
-      <c r="O65" s="32">
+      <c r="O65" s="33">
         <v>6.8</v>
       </c>
-      <c r="P65" s="32">
+      <c r="P65" s="33">
         <v>5.29</v>
       </c>
-      <c r="Q65" s="32">
+      <c r="Q65" s="33">
         <v>6.24</v>
       </c>
-      <c r="R65" s="32">
+      <c r="R65" s="33">
         <v>6.6</v>
       </c>
-      <c r="S65" s="32">
+      <c r="S65" s="33">
         <v>7.09</v>
       </c>
-      <c r="T65" s="32">
+      <c r="T65" s="33">
         <v>10.06</v>
       </c>
-      <c r="U65" s="32">
+      <c r="U65" s="33">
         <v>23.08</v>
       </c>
-      <c r="V65" s="32">
+      <c r="V65" s="33">
         <v>13.22</v>
       </c>
-      <c r="W65" s="32">
+      <c r="W65" s="33">
         <v>9.76</v>
       </c>
-      <c r="X65" s="32">
+      <c r="X65" s="33">
         <v>11.65</v>
       </c>
-      <c r="Y65" s="32">
+      <c r="Y65" s="33">
         <v>33.5</v>
       </c>
-      <c r="Z65" s="32">
+      <c r="Z65" s="33">
         <v>28.9</v>
       </c>
-      <c r="AA65" s="32">
+      <c r="AA65" s="33">
         <v>38.21</v>
       </c>
-      <c r="AB65" s="32">
+      <c r="AB65" s="33">
         <v>18.87</v>
       </c>
-      <c r="AC65" s="31"/>
-      <c r="AD65" s="31"/>
-      <c r="AE65" s="31"/>
-      <c r="AF65" s="31"/>
+      <c r="AC65" s="32"/>
+      <c r="AD65" s="32"/>
+      <c r="AE65" s="32"/>
+      <c r="AF65" s="32"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="30" t="s">
-        <v>504</v>
-      </c>
-      <c r="B66" s="32">
+      <c r="A66" s="31" t="s">
+        <v>505</v>
+      </c>
+      <c r="B66" s="33">
         <v>10.52</v>
       </c>
-      <c r="C66" s="32">
+      <c r="C66" s="33">
         <v>11.29</v>
       </c>
-      <c r="D66" s="32">
+      <c r="D66" s="33">
         <v>12.13</v>
       </c>
-      <c r="E66" s="32">
+      <c r="E66" s="33">
         <v>11.92</v>
       </c>
-      <c r="F66" s="32">
+      <c r="F66" s="33">
         <v>13.27</v>
       </c>
-      <c r="G66" s="32">
+      <c r="G66" s="33">
         <v>13.7</v>
       </c>
-      <c r="H66" s="32">
+      <c r="H66" s="33">
         <v>17.03</v>
       </c>
-      <c r="I66" s="32">
+      <c r="I66" s="33">
         <v>15.93</v>
       </c>
-      <c r="J66" s="32">
+      <c r="J66" s="33">
         <v>16.58</v>
       </c>
-      <c r="K66" s="32">
+      <c r="K66" s="33">
         <v>15.41</v>
       </c>
-      <c r="L66" s="32">
+      <c r="L66" s="33">
         <v>11.43</v>
       </c>
-      <c r="M66" s="32">
+      <c r="M66" s="33">
         <v>7.02</v>
       </c>
-      <c r="N66" s="32">
+      <c r="N66" s="33">
         <v>6.15</v>
       </c>
-      <c r="O66" s="32">
+      <c r="O66" s="33">
         <v>6.32</v>
       </c>
-      <c r="P66" s="32">
+      <c r="P66" s="33">
         <v>6.91</v>
       </c>
-      <c r="Q66" s="32">
+      <c r="Q66" s="33">
         <v>9.07</v>
       </c>
-      <c r="R66" s="32">
+      <c r="R66" s="33">
         <v>10.56</v>
       </c>
-      <c r="S66" s="32">
+      <c r="S66" s="33">
         <v>11.4</v>
       </c>
-      <c r="T66" s="32">
+      <c r="T66" s="33">
         <v>12.56</v>
       </c>
-      <c r="U66" s="32">
+      <c r="U66" s="33">
         <v>16.19</v>
       </c>
-      <c r="V66" s="32">
+      <c r="V66" s="33">
         <v>17.44</v>
       </c>
-      <c r="W66" s="32">
+      <c r="W66" s="33">
         <v>21.18</v>
       </c>
-      <c r="X66" s="32">
+      <c r="X66" s="33">
         <v>25.35</v>
       </c>
-      <c r="Y66" s="31"/>
-      <c r="Z66" s="31"/>
-      <c r="AA66" s="31"/>
-      <c r="AB66" s="31"/>
-      <c r="AC66" s="31"/>
-      <c r="AD66" s="31"/>
-      <c r="AE66" s="31"/>
-      <c r="AF66" s="31"/>
+      <c r="Y66" s="32"/>
+      <c r="Z66" s="32"/>
+      <c r="AA66" s="32"/>
+      <c r="AB66" s="32"/>
+      <c r="AC66" s="32"/>
+      <c r="AD66" s="32"/>
+      <c r="AE66" s="32"/>
+      <c r="AF66" s="32"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="28" t="s">
-        <v>505</v>
-      </c>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-      <c r="P67" s="29"/>
-      <c r="Q67" s="29"/>
-      <c r="R67" s="29"/>
-      <c r="S67" s="29"/>
-      <c r="T67" s="29"/>
-      <c r="U67" s="29"/>
-      <c r="V67" s="29"/>
-      <c r="W67" s="29"/>
-      <c r="X67" s="29"/>
-      <c r="Y67" s="29"/>
-      <c r="Z67" s="29"/>
-      <c r="AA67" s="29"/>
-      <c r="AB67" s="29"/>
-      <c r="AC67" s="29"/>
-      <c r="AD67" s="29"/>
-      <c r="AE67" s="29"/>
-      <c r="AF67" s="29"/>
+      <c r="A67" s="29" t="s">
+        <v>506</v>
+      </c>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="30"/>
+      <c r="T67" s="30"/>
+      <c r="U67" s="30"/>
+      <c r="V67" s="30"/>
+      <c r="W67" s="30"/>
+      <c r="X67" s="30"/>
+      <c r="Y67" s="30"/>
+      <c r="Z67" s="30"/>
+      <c r="AA67" s="30"/>
+      <c r="AB67" s="30"/>
+      <c r="AC67" s="30"/>
+      <c r="AD67" s="30"/>
+      <c r="AE67" s="30"/>
+      <c r="AF67" s="30"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="30" t="s">
-        <v>506</v>
-      </c>
-      <c r="B68" s="32">
+      <c r="A68" s="31" t="s">
+        <v>507</v>
+      </c>
+      <c r="B68" s="33">
         <v>10.24</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="33">
         <v>18.69</v>
       </c>
-      <c r="D68" s="32">
+      <c r="D68" s="33">
         <v>8.65</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="33">
         <v>10.2</v>
       </c>
-      <c r="F68" s="32">
+      <c r="F68" s="33">
         <v>22.09</v>
       </c>
-      <c r="G68" s="32">
+      <c r="G68" s="33">
         <v>13.56</v>
       </c>
-      <c r="H68" s="32">
+      <c r="H68" s="33">
         <v>26.43</v>
       </c>
-      <c r="I68" s="32">
+      <c r="I68" s="33">
         <v>9.52</v>
       </c>
-      <c r="J68" s="32">
+      <c r="J68" s="33">
         <v>17.8</v>
       </c>
-      <c r="K68" s="32">
+      <c r="K68" s="33">
         <v>20.28</v>
       </c>
-      <c r="L68" s="31"/>
-      <c r="M68" s="33">
+      <c r="L68" s="32"/>
+      <c r="M68" s="34">
         <v>390.01</v>
       </c>
-      <c r="N68" s="32">
+      <c r="N68" s="33">
         <v>10.32</v>
       </c>
-      <c r="O68" s="32">
+      <c r="O68" s="33">
         <v>29.93</v>
       </c>
-      <c r="P68" s="32">
+      <c r="P68" s="33">
         <v>9.52</v>
       </c>
-      <c r="Q68" s="32">
+      <c r="Q68" s="33">
         <v>8.35</v>
       </c>
-      <c r="R68" s="32">
+      <c r="R68" s="33">
         <v>11.16</v>
       </c>
-      <c r="S68" s="32">
+      <c r="S68" s="33">
         <v>11.42</v>
       </c>
-      <c r="T68" s="32">
+      <c r="T68" s="33">
         <v>13.99</v>
       </c>
-      <c r="U68" s="32">
+      <c r="U68" s="33">
         <v>52.12</v>
       </c>
-      <c r="V68" s="32">
+      <c r="V68" s="33">
         <v>18.67</v>
       </c>
-      <c r="W68" s="32">
+      <c r="W68" s="33">
         <v>11.05</v>
       </c>
-      <c r="X68" s="32">
+      <c r="X68" s="33">
         <v>26.95</v>
       </c>
-      <c r="Y68" s="33">
+      <c r="Y68" s="34">
         <v>176.25</v>
       </c>
-      <c r="Z68" s="32">
+      <c r="Z68" s="33">
         <v>72.7</v>
       </c>
-      <c r="AA68" s="32">
+      <c r="AA68" s="33">
         <v>96.16</v>
       </c>
-      <c r="AB68" s="31"/>
-      <c r="AC68" s="31"/>
-      <c r="AD68" s="31"/>
-      <c r="AE68" s="31"/>
-      <c r="AF68" s="31"/>
+      <c r="AB68" s="32"/>
+      <c r="AC68" s="32"/>
+      <c r="AD68" s="32"/>
+      <c r="AE68" s="32"/>
+      <c r="AF68" s="32"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="30" t="s">
-        <v>507</v>
-      </c>
-      <c r="B69" s="32">
+      <c r="A69" s="31" t="s">
+        <v>508</v>
+      </c>
+      <c r="B69" s="33">
         <v>12.63</v>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="33">
         <v>13.68</v>
       </c>
-      <c r="D69" s="32">
+      <c r="D69" s="33">
         <v>14.7</v>
       </c>
-      <c r="E69" s="32">
+      <c r="E69" s="33">
         <v>14.33</v>
       </c>
-      <c r="F69" s="32">
+      <c r="F69" s="33">
         <v>15.76</v>
       </c>
-      <c r="G69" s="32">
+      <c r="G69" s="33">
         <v>15.89</v>
       </c>
-      <c r="H69" s="32">
+      <c r="H69" s="33">
         <v>25.19</v>
       </c>
-      <c r="I69" s="32">
+      <c r="I69" s="33">
         <v>27.44</v>
       </c>
-      <c r="J69" s="32">
+      <c r="J69" s="33">
         <v>37.37</v>
       </c>
-      <c r="K69" s="32">
+      <c r="K69" s="33">
         <v>59.23</v>
       </c>
-      <c r="L69" s="32">
+      <c r="L69" s="33">
         <v>63.36</v>
       </c>
-      <c r="M69" s="32">
+      <c r="M69" s="33">
         <v>13.94</v>
       </c>
-      <c r="N69" s="32">
+      <c r="N69" s="33">
         <v>10.82</v>
       </c>
-      <c r="O69" s="32">
+      <c r="O69" s="33">
         <v>11.08</v>
       </c>
-      <c r="P69" s="32">
+      <c r="P69" s="33">
         <v>10.74</v>
       </c>
-      <c r="Q69" s="32">
+      <c r="Q69" s="33">
         <v>14.02</v>
       </c>
-      <c r="R69" s="32">
+      <c r="R69" s="33">
         <v>16.75</v>
       </c>
-      <c r="S69" s="32">
+      <c r="S69" s="33">
         <v>16.33</v>
       </c>
-      <c r="T69" s="32">
+      <c r="T69" s="33">
         <v>18.71</v>
       </c>
-      <c r="U69" s="32">
+      <c r="U69" s="33">
         <v>27.4</v>
       </c>
-      <c r="V69" s="32">
+      <c r="V69" s="33">
         <v>30.17</v>
       </c>
-      <c r="W69" s="32">
+      <c r="W69" s="33">
         <v>40.48</v>
       </c>
-      <c r="X69" s="31"/>
-      <c r="Y69" s="31"/>
-      <c r="Z69" s="31"/>
-      <c r="AA69" s="31"/>
-      <c r="AB69" s="31"/>
-      <c r="AC69" s="31"/>
-      <c r="AD69" s="31"/>
-      <c r="AE69" s="31"/>
-      <c r="AF69" s="31"/>
+      <c r="X69" s="32"/>
+      <c r="Y69" s="32"/>
+      <c r="Z69" s="32"/>
+      <c r="AA69" s="32"/>
+      <c r="AB69" s="32"/>
+      <c r="AC69" s="32"/>
+      <c r="AD69" s="32"/>
+      <c r="AE69" s="32"/>
+      <c r="AF69" s="32"/>
     </row>
     <row r="70" ht="15.75" customHeight="1"/>
     <row r="71" ht="15.75" customHeight="1"/>
